--- a/output/ICP Q2'26.xlsx
+++ b/output/ICP Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F166"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -544,10 +544,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1634</v>
+        <v>-1541</v>
       </c>
       <c r="D5" t="n">
-        <v>-1634</v>
+        <v>-1541</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -628,10 +628,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1767.57</v>
+        <v>-1689.57</v>
       </c>
       <c r="D8" t="n">
-        <v>-1768</v>
+        <v>-1690</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -712,10 +712,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1885.04</v>
+        <v>-1964.04</v>
       </c>
       <c r="D11" t="n">
-        <v>-1885</v>
+        <v>-1964</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -796,10 +796,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-4026.02</v>
+        <v>-4035.02</v>
       </c>
       <c r="D14" t="n">
-        <v>-4026</v>
+        <v>-4035</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -880,10 +880,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-372.36</v>
+        <v>-390.36</v>
       </c>
       <c r="D17" t="n">
-        <v>-372</v>
+        <v>-390</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1188,10 +1188,10 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-2382.3</v>
+        <v>-2567.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-2382</v>
+        <v>-2567</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1216,10 +1216,10 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-35670.77</v>
+        <v>-35927.77</v>
       </c>
       <c r="D29" t="n">
-        <v>-35671</v>
+        <v>-35928</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1356,10 +1356,10 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-628.84</v>
+        <v>-712.84</v>
       </c>
       <c r="D34" t="n">
-        <v>-629</v>
+        <v>-713</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1412,10 +1412,10 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-3126.81</v>
+        <v>-3569.81</v>
       </c>
       <c r="D36" t="n">
-        <v>-3127</v>
+        <v>-3570</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1440,10 +1440,10 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-4315.16</v>
+        <v>-4357.16</v>
       </c>
       <c r="D37" t="n">
-        <v>-4315</v>
+        <v>-4357</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1720,10 +1720,10 @@
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-4395.84</v>
+        <v>-4721.84</v>
       </c>
       <c r="D47" t="n">
-        <v>-4396</v>
+        <v>-4722</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -1860,10 +1860,10 @@
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-3275.88</v>
+        <v>-3310.88</v>
       </c>
       <c r="D52" t="n">
-        <v>-3276</v>
+        <v>-3311</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -1916,10 +1916,10 @@
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-346.74</v>
+        <v>-617.74</v>
       </c>
       <c r="D54" t="n">
-        <v>-347</v>
+        <v>-618</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -1972,10 +1972,10 @@
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-7741.44</v>
+        <v>-7939.44</v>
       </c>
       <c r="D56" t="n">
-        <v>-7741</v>
+        <v>-7939</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2112,10 +2112,10 @@
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1220.34</v>
+        <v>-1437.91</v>
       </c>
       <c r="D61" t="n">
-        <v>-1220</v>
+        <v>-1438</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2131,51 +2131,51 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">               945</t>
+          <t xml:space="preserve">               382</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>AMARO Travel GmbH</t>
+          <t>THENAMARIS SHIPS MANAGEMENT INC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-53.6</v>
+        <v>-22</v>
       </c>
       <c r="D62" t="n">
-        <v>-54</v>
+        <v>-22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DE309139121</t>
+          <t>EL098010844</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>GREECE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2450</t>
+          <t xml:space="preserve">               945</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Air Partner International GmbH</t>
+          <t>AMARO Travel GmbH</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-672.04</v>
+        <v>-53.6</v>
       </c>
       <c r="D63" t="n">
-        <v>-672</v>
+        <v>-54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DE184629207</t>
+          <t>DE309139121</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2187,23 +2187,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1576</t>
+          <t xml:space="preserve">              2450</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Andreas Zerr</t>
+          <t>Air Partner International GmbH</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-173.2</v>
+        <v>-672.04</v>
       </c>
       <c r="D64" t="n">
-        <v>-173</v>
+        <v>-672</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DE221230922</t>
+          <t>DE184629207</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2215,23 +2215,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">               152</t>
+          <t xml:space="preserve">              1576</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Axxaz Europe GmbH</t>
+          <t>Andreas Zerr</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-19151.99</v>
+        <v>-173.2</v>
       </c>
       <c r="D65" t="n">
-        <v>-19152</v>
+        <v>-173</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DE296988120</t>
+          <t>DE221230922</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2243,23 +2243,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2319</t>
+          <t xml:space="preserve">               152</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
+          <t>Axxaz Europe GmbH</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-53</v>
+        <v>-19230.99</v>
       </c>
       <c r="D66" t="n">
-        <v>-53</v>
+        <v>-19231</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DE249771948</t>
+          <t>DE296988120</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2271,23 +2271,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2318</t>
+          <t xml:space="preserve">              2736</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
+          <t>Beteiligungsgesellschaft MS Santa Vanessa mbH &amp; Co</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="D67" t="n">
-        <v>-21</v>
+        <v>-23</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DE213881581</t>
+          <t>DE232610165</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2299,23 +2299,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2594</t>
+          <t xml:space="preserve">              2319</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG forRDO Endeavour - 2522</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-196.47</v>
+        <v>-85</v>
       </c>
       <c r="D68" t="n">
-        <v>-196</v>
+        <v>-85</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DE307865976</t>
+          <t>DE249771948</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2327,23 +2327,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2107</t>
+          <t xml:space="preserve">              2318</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-2683.32</v>
+        <v>-42</v>
       </c>
       <c r="D69" t="n">
-        <v>-2683</v>
+        <v>-42</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DE293561563</t>
+          <t>DE213881581</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2355,23 +2355,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">               197</t>
+          <t xml:space="preserve">              2594</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>DS Crewing Sevices GmbH</t>
+          <t>CPO Crewing GmbH &amp; Co. KG forRDO Endeavour - 2522</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-30</v>
+        <v>-196.47</v>
       </c>
       <c r="D70" t="n">
-        <v>-30</v>
+        <v>-196</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DE318346366</t>
+          <t>DE307865976</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2383,23 +2383,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1553</t>
+          <t xml:space="preserve">              2107</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Davit-Company GmbH &amp; W. Harms</t>
+          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-96.31999999999999</v>
+        <v>-2683.32</v>
       </c>
       <c r="D71" t="n">
-        <v>-96</v>
+        <v>-2683</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DE291870147</t>
+          <t>DE293561563</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2411,23 +2411,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1169</t>
+          <t xml:space="preserve">               197</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>EMS Crewing GmbH</t>
+          <t>DS Crewing Sevices GmbH</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-146</v>
+        <v>-30</v>
       </c>
       <c r="D72" t="n">
-        <v>-146</v>
+        <v>-30</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DE262060886</t>
+          <t>DE318346366</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2439,23 +2439,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2452</t>
+          <t xml:space="preserve">              1553</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>F.Laeisz GmbH Hamburg</t>
+          <t>Davit-Company GmbH &amp; W. Harms</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-53.6</v>
+        <v>-96.31999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-54</v>
+        <v>-96</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DE170925486</t>
+          <t>DE291870147</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2467,23 +2467,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">               231</t>
+          <t xml:space="preserve">              1169</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GP Care Solutions GmbH</t>
+          <t>EMS Crewing GmbH</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-1540.93</v>
+        <v>-146</v>
       </c>
       <c r="D74" t="n">
-        <v>-1541</v>
+        <v>-146</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DE322179714</t>
+          <t>DE262060886</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2495,23 +2495,23 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">               601</t>
+          <t xml:space="preserve">              2452</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GoodCrew GmbH</t>
+          <t>F.Laeisz GmbH Hamburg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-2664.29</v>
+        <v>-53.6</v>
       </c>
       <c r="D75" t="n">
-        <v>-2664</v>
+        <v>-54</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DE326784905</t>
+          <t>DE170925486</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -2523,23 +2523,23 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2284</t>
+          <t xml:space="preserve">               231</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Hansa Safety Services GmbH</t>
+          <t>GP Care Solutions GmbH</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1021.05</v>
+        <v>-1540.93</v>
       </c>
       <c r="D76" t="n">
-        <v>-1021</v>
+        <v>-1541</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DE284814823</t>
+          <t>DE322179714</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -2551,23 +2551,23 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1146</t>
+          <t xml:space="preserve">               601</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>KG MS 2. CPO Livorno Offen Reederei GmbH &amp; Co. c/o</t>
+          <t>GoodCrew GmbH</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-25</v>
+        <v>-2664.29</v>
       </c>
       <c r="D77" t="n">
-        <v>-25</v>
+        <v>-2664</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DE322053391</t>
+          <t>DE326784905</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -2579,23 +2579,23 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1145</t>
+          <t xml:space="preserve">              2284</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>KG MS CPO LA SPEZIA Offen Reederei UG (haftungsbes</t>
+          <t>Hansa Safety Services GmbH</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-335</v>
+        <v>-1085.05</v>
       </c>
       <c r="D78" t="n">
-        <v>-335</v>
+        <v>-1085</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DE298771680</t>
+          <t>DE284814823</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -2607,23 +2607,23 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2376</t>
+          <t xml:space="preserve">              1146</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
+          <t>KG MS 2. CPO Livorno Offen Reederei GmbH &amp; Co. c/o</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-46</v>
+        <v>-25</v>
       </c>
       <c r="D79" t="n">
-        <v>-46</v>
+        <v>-25</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DE257260686</t>
+          <t>DE322053391</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -2635,23 +2635,23 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1144</t>
+          <t xml:space="preserve">              1145</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KG MS CPO VENEZIA Offen Reederei GmbH &amp; Co. c/o CP</t>
+          <t>KG MS CPO LA SPEZIA Offen Reederei UG (haftungsbes</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-186.61</v>
+        <v>-383</v>
       </c>
       <c r="D80" t="n">
-        <v>-187</v>
+        <v>-383</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DE256596537</t>
+          <t>DE298771680</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -2663,23 +2663,23 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2015</t>
+          <t xml:space="preserve">              2376</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KG MS Santa Viola Offen Reederei GmbH &amp; Co. c/o CP</t>
+          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-25</v>
+        <v>-46</v>
       </c>
       <c r="D81" t="n">
-        <v>-25</v>
+        <v>-46</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DE230140293</t>
+          <t>DE257260686</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -2691,23 +2691,23 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1435</t>
+          <t xml:space="preserve">              1144</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>M2L Pacific S.A.</t>
+          <t>KG MS CPO VENEZIA Offen Reederei GmbH &amp; Co. c/o CP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-1596.11</v>
+        <v>-186.61</v>
       </c>
       <c r="D82" t="n">
-        <v>-1596</v>
+        <v>-187</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DE811585869</t>
+          <t>DE256596537</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -2719,23 +2719,23 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1916</t>
+          <t xml:space="preserve">              2015</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>MS "Paganella 2" GmbH &amp; Co. KG</t>
+          <t>KG MS Santa Viola Offen Reederei GmbH &amp; Co. c/o CP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-26.8</v>
+        <v>-25</v>
       </c>
       <c r="D83" t="n">
-        <v>-27</v>
+        <v>-25</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DE292632581</t>
+          <t>DE230140293</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -2747,23 +2747,23 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1856</t>
+          <t xml:space="preserve">              1435</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>MS "Pagna" GmbH &amp; Co. KG</t>
+          <t>M2L Pacific S.A.</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-75</v>
+        <v>-1596.11</v>
       </c>
       <c r="D84" t="n">
-        <v>-75</v>
+        <v>-1596</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DE261459100</t>
+          <t>DE811585869</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -2775,23 +2775,23 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1548</t>
+          <t xml:space="preserve">              1916</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MS "PolarPacific" GmbH &amp; Co. KG</t>
+          <t>MS "Paganella 2" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-260.01</v>
+        <v>-26.8</v>
       </c>
       <c r="D85" t="n">
-        <v>-260</v>
+        <v>-27</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DE275633887</t>
+          <t>DE292632581</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -2803,23 +2803,23 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2859</t>
+          <t xml:space="preserve">              1856</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MS BSG Bimini GmbH &amp; Co.KG  c/o CPO Crewing GmbH &amp;</t>
+          <t>MS "Pagna" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="D86" t="n">
-        <v>-25</v>
+        <v>-75</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DE346013071</t>
+          <t>DE261459100</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -2831,23 +2831,23 @@
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2684</t>
+          <t xml:space="preserve">              1548</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Martide Holding GmbH</t>
+          <t>MS "PolarPacific" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>16.52</v>
+        <v>-260.01</v>
       </c>
       <c r="D87" t="n">
-        <v>17</v>
+        <v>-260</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DE450210277</t>
+          <t>DE275633887</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -2859,23 +2859,23 @@
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">               309</t>
+          <t xml:space="preserve">              2859</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>NSB Crewing Solutions</t>
+          <t>MS BSG Bimini GmbH &amp; Co.KG  c/o CPO Crewing GmbH &amp;</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-4881.02</v>
+        <v>-25</v>
       </c>
       <c r="D88" t="n">
-        <v>-4881</v>
+        <v>-25</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DE283269969</t>
+          <t>DE346013071</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -2887,23 +2887,23 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">               310</t>
+          <t xml:space="preserve">              2684</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>NSB Reederei GmbH &amp; Co. Kg</t>
+          <t>Martide Holding GmbH</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-843.41</v>
+        <v>16.52</v>
       </c>
       <c r="D89" t="n">
-        <v>-843</v>
+        <v>17</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DE116474094</t>
+          <t>DE450210277</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -2915,23 +2915,23 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2238</t>
+          <t xml:space="preserve">               309</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
+          <t>NSB Crewing Solutions</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-121.4</v>
+        <v>-4881.02</v>
       </c>
       <c r="D90" t="n">
-        <v>-121</v>
+        <v>-4881</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DE362363142</t>
+          <t>DE283269969</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -2943,23 +2943,23 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">               298</t>
+          <t xml:space="preserve">               310</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Nordic Hamburg Crewing Services GmbH</t>
+          <t>NSB Reederei GmbH &amp; Co. Kg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-30944</v>
+        <v>-843.41</v>
       </c>
       <c r="D91" t="n">
-        <v>-30944</v>
+        <v>-843</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DE309948810</t>
+          <t>DE116474094</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -2971,23 +2971,23 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2678</t>
+          <t xml:space="preserve">              2238</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
+          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-2154.4</v>
+        <v>-121.4</v>
       </c>
       <c r="D92" t="n">
-        <v>-2154</v>
+        <v>-121</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DE285660591</t>
+          <t>DE362363142</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -2999,23 +2999,23 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3088</t>
+          <t xml:space="preserve">               298</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nordic Tokyo GmbH &amp; Co. KG c/o Nordic Cruise Manag</t>
+          <t>Nordic Hamburg Crewing Services GmbH</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-182.4</v>
+        <v>-31386</v>
       </c>
       <c r="D93" t="n">
-        <v>-182</v>
+        <v>-31386</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DE451301791</t>
+          <t>DE309948810</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3027,23 +3027,23 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3064</t>
+          <t xml:space="preserve">              2678</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>OBC by Avico GmbH</t>
+          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-573.39</v>
+        <v>-2397.4</v>
       </c>
       <c r="D94" t="n">
-        <v>-573</v>
+        <v>-2397</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DE457137561</t>
+          <t>DE285660591</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3055,23 +3055,23 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3017</t>
+          <t xml:space="preserve">              3088</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SUNDAIR Gmbh</t>
+          <t>Nordic Tokyo GmbH &amp; Co. KG c/o Nordic Cruise Manag</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-192</v>
+        <v>-182.4</v>
       </c>
       <c r="D95" t="n">
-        <v>-192</v>
+        <v>-182</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DE305307186</t>
+          <t>DE451301791</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3083,23 +3083,23 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">               496</t>
+          <t xml:space="preserve">              3064</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Scheibert &amp; Meissner Personalberatung GbR</t>
+          <t>OBC by Avico GmbH</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-75</v>
+        <v>-573.39</v>
       </c>
       <c r="D96" t="n">
-        <v>-75</v>
+        <v>-573</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DE240712065</t>
+          <t>DE457137561</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3111,23 +3111,23 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3026</t>
+          <t xml:space="preserve">              3017</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>T &amp; T In Situ Machining GmbH</t>
+          <t>SUNDAIR Gmbh</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-420.94</v>
+        <v>-192</v>
       </c>
       <c r="D97" t="n">
-        <v>-421</v>
+        <v>-192</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DE327579122</t>
+          <t>DE305307186</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3139,23 +3139,23 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">               832</t>
+          <t xml:space="preserve">               496</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>UHL Chartering GmbH &amp; Co. KG</t>
+          <t>Scheibert &amp; Meissner Personalberatung GbR</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-1446.3</v>
+        <v>-75</v>
       </c>
       <c r="D98" t="n">
-        <v>-1446</v>
+        <v>-75</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DE350330837</t>
+          <t>DE240712065</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3167,23 +3167,23 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1065</t>
+          <t xml:space="preserve">              3026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>UHL Crewing GmbH</t>
+          <t>T &amp; T In Situ Machining GmbH</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-5501.64</v>
+        <v>-543.9400000000001</v>
       </c>
       <c r="D99" t="n">
-        <v>-5502</v>
+        <v>-544</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DE330510394</t>
+          <t>DE327579122</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3195,23 +3195,23 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">               396</t>
+          <t xml:space="preserve">               832</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>USC Crew GmbH</t>
+          <t>UHL Chartering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-10788.82</v>
+        <v>-1446.3</v>
       </c>
       <c r="D100" t="n">
-        <v>-10789</v>
+        <v>-1446</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>DE274971782</t>
+          <t>DE350330837</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3223,23 +3223,23 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3065</t>
+          <t xml:space="preserve">              1065</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>USC GmbH</t>
+          <t>UHL Crewing GmbH</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-2638.95</v>
+        <v>-5623.64</v>
       </c>
       <c r="D101" t="n">
-        <v>-2639</v>
+        <v>-5624</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>DE334043640</t>
+          <t>DE330510394</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3251,23 +3251,23 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">               397</t>
+          <t xml:space="preserve">               396</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>UVIS UG (haftungsbeschraenkt)</t>
+          <t>USC Crew GmbH</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-1187.48</v>
+        <v>-10792.82</v>
       </c>
       <c r="D102" t="n">
-        <v>-1187</v>
+        <v>-10793</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DE319612386</t>
+          <t>DE274971782</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3279,23 +3279,23 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">               395</t>
+          <t xml:space="preserve">              3065</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>United Engineering Solutions GmbH</t>
+          <t>USC GmbH</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>24</v>
+        <v>-2638.95</v>
       </c>
       <c r="D103" t="n">
-        <v>24</v>
+        <v>-2639</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DE319531170</t>
+          <t>DE334043640</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -3307,23 +3307,23 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">               867</t>
+          <t xml:space="preserve">               397</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>United Heavy Lift GmbH &amp; Co. KG</t>
+          <t>UVIS UG (haftungsbeschraenkt)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1641.09</v>
+        <v>-1187.48</v>
       </c>
       <c r="D104" t="n">
-        <v>-1641</v>
+        <v>-1187</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DE350330845</t>
+          <t>DE319612386</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -3335,23 +3335,23 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">               637</t>
+          <t xml:space="preserve">               395</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>over-C Crewing GmbH &amp; Co. KG</t>
+          <t>United Engineering Solutions GmbH</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-1203.67</v>
+        <v>24</v>
       </c>
       <c r="D105" t="n">
-        <v>-1204</v>
+        <v>24</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DE321517652</t>
+          <t>DE319531170</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -3363,359 +3363,359 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2295</t>
+          <t xml:space="preserve">               867</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
+          <t>United Heavy Lift GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-25</v>
+        <v>-1667.09</v>
       </c>
       <c r="D106" t="n">
-        <v>-25</v>
+        <v>-1667</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>EL801158466</t>
+          <t>DE350330845</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2655</t>
+          <t xml:space="preserve">               637</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>THALPIS CRS SA</t>
+          <t>over-C Crewing GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-117.69</v>
+        <v>-1203.67</v>
       </c>
       <c r="D107" t="n">
-        <v>-118</v>
+        <v>-1204</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>EL996435463</t>
+          <t>DE321517652</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3111</t>
+          <t xml:space="preserve">              2295</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Arion Retail Group Hungary KFT</t>
+          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-87.78</v>
+        <v>-281</v>
       </c>
       <c r="D108" t="n">
-        <v>-88</v>
+        <v>-281</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>HU32887413</t>
+          <t>EL801158466</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1952</t>
+          <t xml:space="preserve">               896</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Fleet Air International Kft.</t>
+          <t>SRS WHOLESALE (RE)INSURANCE BROKERS A.E.</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-2080.78</v>
+        <v>-264</v>
       </c>
       <c r="D109" t="n">
-        <v>-2081</v>
+        <v>-264</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>HU13819822</t>
+          <t>EL801153262</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2486</t>
+          <t xml:space="preserve">              2655</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Alpha Marine</t>
+          <t>THALPIS CRS SA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-325.4</v>
+        <v>-117.69</v>
       </c>
       <c r="D110" t="n">
-        <v>-325</v>
+        <v>-118</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>IE3417853KH</t>
+          <t>EL996435463</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2927</t>
+          <t xml:space="preserve">              3111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>FLY4 Airlines Green Limited</t>
+          <t>Arion Retail Group Hungary KFT</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-18274.84</v>
+        <v>-87.78</v>
       </c>
       <c r="D111" t="n">
-        <v>-18275</v>
+        <v>-88</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>IE4197556QH</t>
+          <t>HU32887413</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">               319</t>
+          <t xml:space="preserve">              1952</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Pacific Blue Ltd</t>
+          <t>Fleet Air International Kft.</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-5628.06</v>
+        <v>-2080.78</v>
       </c>
       <c r="D112" t="n">
-        <v>-5628</v>
+        <v>-2081</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>IE6333494O</t>
+          <t>HU13819822</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2040</t>
+          <t xml:space="preserve">              2486</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
+          <t>Alpha Marine</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-581.6</v>
+        <v>-325.4</v>
       </c>
       <c r="D113" t="n">
-        <v>-582</v>
+        <v>-325</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IT02122640994</t>
+          <t>IE3417853KH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1529</t>
+          <t xml:space="preserve">              2927</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OMEGA S.R.L.</t>
+          <t>FLY4 Airlines Green Limited</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-47.75</v>
+        <v>-18409.84</v>
       </c>
       <c r="D114" t="n">
-        <v>-48</v>
+        <v>-18410</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IT02343130270</t>
+          <t>IE4197556QH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">                34</t>
+          <t xml:space="preserve">               319</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>C Teleport AS</t>
+          <t>Pacific Blue Ltd</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-228283.32</v>
+        <v>-5628.06</v>
       </c>
       <c r="D115" t="n">
-        <v>-228283</v>
+        <v>-5628</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>LV40203039827</t>
+          <t>IE6333494O</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">                85</t>
+          <t xml:space="preserve">              2040</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Crewplanet SIA</t>
+          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-90445.46000000001</v>
+        <v>-581.6</v>
       </c>
       <c r="D116" t="n">
-        <v>-90445</v>
+        <v>-582</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>LV40003789592</t>
+          <t>IT02122640994</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">               907</t>
+          <t xml:space="preserve">              1529</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>HANSAEL SIA</t>
+          <t>OMEGA S.R.L.</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-25</v>
+        <v>-47.75</v>
       </c>
       <c r="D117" t="n">
-        <v>-25</v>
+        <v>-48</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>LV40003660806</t>
+          <t>IT02343130270</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2805</t>
+          <t xml:space="preserve">                34</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Martide Manning Latvia SIA</t>
+          <t>C Teleport AS</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-198</v>
+        <v>-228283.32</v>
       </c>
       <c r="D118" t="n">
-        <v>-198</v>
+        <v>-228283</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LV40203626599</t>
+          <t>LV40203039827</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -3727,23 +3727,23 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">               340</t>
+          <t xml:space="preserve">                85</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>RIX Shipmanagement LTD</t>
+          <t>Crewplanet SIA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-15969.25</v>
+        <v>-93718.46000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>-15969</v>
+        <v>-93718</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LV40103681236</t>
+          <t>LV40003789592</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -3755,23 +3755,23 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">               751</t>
+          <t xml:space="preserve">               907</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>SIA OJ CREW RIGA</t>
+          <t>HANSAEL SIA</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="D120" t="n">
-        <v>25</v>
+        <v>-25</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LV50203144731</t>
+          <t>LV40003660806</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -3783,23 +3783,23 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2420</t>
+          <t xml:space="preserve">              2805</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>SIA OJ Travel</t>
+          <t>Martide Manning Latvia SIA</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-15578.39</v>
+        <v>-198</v>
       </c>
       <c r="D121" t="n">
-        <v>-15578</v>
+        <v>-198</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LV40003286572</t>
+          <t>LV40203626599</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -3811,23 +3811,23 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1091</t>
+          <t xml:space="preserve">               340</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>UNION AVIATION AS</t>
+          <t>RIX Shipmanagement LTD</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-8950.35</v>
+        <v>-15969.25</v>
       </c>
       <c r="D122" t="n">
-        <v>-8950</v>
+        <v>-15969</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LV40203294676</t>
+          <t>LV40103681236</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -3839,191 +3839,191 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2742</t>
+          <t xml:space="preserve">               751</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>BALTNAUTIC SHIPPING LTD</t>
+          <t>SIA OJ CREW RIGA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-1422.44</v>
+        <v>25</v>
       </c>
       <c r="D123" t="n">
-        <v>-1422</v>
+        <v>25</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LT417071917</t>
+          <t>LV50203144731</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">               569</t>
+          <t xml:space="preserve">              2420</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>GEO@SEA Luxembourg S.A.</t>
+          <t>SIA OJ Travel</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-6290.82</v>
+        <v>-15578.39</v>
       </c>
       <c r="D124" t="n">
-        <v>-6291</v>
+        <v>-15578</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LU32235384</t>
+          <t>LV40003286572</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2964</t>
+          <t xml:space="preserve">              1091</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>MV KAREWOOD BRAVE — IMO 9281516</t>
+          <t>UNION AVIATION AS</t>
         </is>
       </c>
       <c r="C125" t="n">
-        <v>-60</v>
+        <v>-8950.35</v>
       </c>
       <c r="D125" t="n">
-        <v>-60</v>
+        <v>-8950</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>MT24502936</t>
+          <t>LV40203294676</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>MALTA</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t xml:space="preserve">               862</t>
+          <t xml:space="preserve">              2742</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Atlantis Tankers Group (Malta) Ltd.</t>
+          <t>BALTNAUTIC SHIPPING LTD</t>
         </is>
       </c>
       <c r="C126" t="n">
-        <v>-344.24</v>
+        <v>-1422.44</v>
       </c>
       <c r="D126" t="n">
-        <v>-344</v>
+        <v>-1422</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>MT21829715</t>
+          <t>LT417071917</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Lithuania</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1465</t>
+          <t xml:space="preserve">               569</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>CldN Malta Ltd.</t>
+          <t>GEO@SEA Luxembourg S.A.</t>
         </is>
       </c>
       <c r="C127" t="n">
-        <v>-28286.51</v>
+        <v>-6290.82</v>
       </c>
       <c r="D127" t="n">
-        <v>-28287</v>
+        <v>-6291</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>MT22140026</t>
+          <t>LU32235384</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Luxembourg</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1415</t>
+          <t xml:space="preserve">              2964</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>DC Aviation Ltd.</t>
+          <t>MV KAREWOOD BRAVE — IMO 9281516</t>
         </is>
       </c>
       <c r="C128" t="n">
-        <v>-1023.68</v>
+        <v>-60</v>
       </c>
       <c r="D128" t="n">
-        <v>-1024</v>
+        <v>-60</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>MT18886308</t>
+          <t>MT24502936</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>MALTA</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2194</t>
+          <t xml:space="preserve">               862</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Elit’Avia Malta Ltd</t>
+          <t>Atlantis Tankers Group (Malta) Ltd.</t>
         </is>
       </c>
       <c r="C129" t="n">
-        <v>-5560.25</v>
+        <v>-344.24</v>
       </c>
       <c r="D129" t="n">
-        <v>-5560</v>
+        <v>-344</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>MT19960414</t>
+          <t>MT21829715</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4035,23 +4035,23 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t xml:space="preserve">               218</t>
+          <t xml:space="preserve">              1465</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FT Portoria Tankers Ltd</t>
+          <t>CldN Malta Ltd.</t>
         </is>
       </c>
       <c r="C130" t="n">
-        <v>-351.6</v>
+        <v>-28320.51</v>
       </c>
       <c r="D130" t="n">
-        <v>-352</v>
+        <v>-28321</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>MT22398518</t>
+          <t>MT22140026</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4063,23 +4063,23 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t xml:space="preserve">               718</t>
+          <t xml:space="preserve">              1415</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Furtrans Tanker Holdings Ltd</t>
+          <t>DC Aviation Ltd.</t>
         </is>
       </c>
       <c r="C131" t="n">
-        <v>-2328.7</v>
+        <v>-1023.68</v>
       </c>
       <c r="D131" t="n">
-        <v>-2329</v>
+        <v>-1024</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>MT26731101</t>
+          <t>MT18886308</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -4091,23 +4091,23 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2408</t>
+          <t xml:space="preserve">              2194</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Hans Travel Ltd</t>
+          <t>Elit’Avia Malta Ltd</t>
         </is>
       </c>
       <c r="C132" t="n">
-        <v>250</v>
+        <v>-5560.25</v>
       </c>
       <c r="D132" t="n">
-        <v>250</v>
+        <v>-5560</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>MT28450014</t>
+          <t>MT19960414</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -4119,23 +4119,23 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2939</t>
+          <t xml:space="preserve">               218</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Lighthouse Yachting Malta Limited</t>
+          <t>FT Portoria Tankers Ltd</t>
         </is>
       </c>
       <c r="C133" t="n">
-        <v>-246.52</v>
+        <v>-351.6</v>
       </c>
       <c r="D133" t="n">
-        <v>-247</v>
+        <v>-352</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>MT29674336</t>
+          <t>MT22398518</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -4147,23 +4147,23 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2963</t>
+          <t xml:space="preserve">               718</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>MV KAREWOOD GLORY — IMO 9281504</t>
+          <t>Furtrans Tanker Holdings Ltd</t>
         </is>
       </c>
       <c r="C134" t="n">
-        <v>-177.78</v>
+        <v>-2381.7</v>
       </c>
       <c r="D134" t="n">
-        <v>-178</v>
+        <v>-2382</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>MT24503928</t>
+          <t>MT26731101</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -4175,23 +4175,23 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2995</t>
+          <t xml:space="preserve">              2408</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>MV KAREWOOD PRIDE — IMO 9281499</t>
+          <t>Hans Travel Ltd</t>
         </is>
       </c>
       <c r="C135" t="n">
-        <v>-90</v>
+        <v>250</v>
       </c>
       <c r="D135" t="n">
-        <v>-90</v>
+        <v>250</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>MT24503035</t>
+          <t>MT28450014</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -4203,23 +4203,23 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2992</t>
+          <t xml:space="preserve">              2939</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>MV KAREWOOD STAR — IMO 9363986</t>
+          <t>Lighthouse Yachting Malta Limited</t>
         </is>
       </c>
       <c r="C136" t="n">
-        <v>-107.81</v>
+        <v>-246.52</v>
       </c>
       <c r="D136" t="n">
-        <v>-108</v>
+        <v>-247</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>MT24503217</t>
+          <t>MT29674336</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -4231,23 +4231,23 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2037</t>
+          <t xml:space="preserve">              2963</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
+          <t>MV KAREWOOD GLORY — IMO 9281504</t>
         </is>
       </c>
       <c r="C137" t="n">
-        <v>-1030.85</v>
+        <v>-177.78</v>
       </c>
       <c r="D137" t="n">
-        <v>-1031</v>
+        <v>-178</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>MT27270636</t>
+          <t>MT24503928</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
@@ -4259,23 +4259,23 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2036</t>
+          <t xml:space="preserve">              2995</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Quinto Tankers Ltd</t>
+          <t>MV KAREWOOD PRIDE — IMO 9281499</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>-535.17</v>
+        <v>-90</v>
       </c>
       <c r="D138" t="n">
-        <v>-535</v>
+        <v>-90</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>MT27591013</t>
+          <t>MT24503035</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -4287,23 +4287,23 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t xml:space="preserve">               826</t>
+          <t xml:space="preserve">              2992</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>SL Ship Management Ltd</t>
+          <t>MV KAREWOOD STAR — IMO 9363986</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>-1589.04</v>
+        <v>-107.81</v>
       </c>
       <c r="D139" t="n">
-        <v>-1589</v>
+        <v>-108</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>MT18726720</t>
+          <t>MT24503217</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -4315,23 +4315,23 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2105</t>
+          <t xml:space="preserve">              2037</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>ZuluWaves Limited</t>
+          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
         </is>
       </c>
       <c r="C140" t="n">
-        <v>-2410.24</v>
+        <v>-1030.85</v>
       </c>
       <c r="D140" t="n">
-        <v>-2410</v>
+        <v>-1031</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>MT30851503</t>
+          <t>MT27270636</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
@@ -4343,135 +4343,135 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3110</t>
+          <t xml:space="preserve">              2036</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Arion Retail Group Poland Sp. z o.o.</t>
+          <t>Quinto Tankers Ltd</t>
         </is>
       </c>
       <c r="C141" t="n">
-        <v>-18</v>
+        <v>-535.17</v>
       </c>
       <c r="D141" t="n">
-        <v>-18</v>
+        <v>-535</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>PL5253064487</t>
+          <t>MT27591013</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Poland</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t xml:space="preserve">               679</t>
+          <t xml:space="preserve">               826</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>Afonso Ferreira Faria unipessoal LDa</t>
+          <t>SL Ship Management Ltd</t>
         </is>
       </c>
       <c r="C142" t="n">
-        <v>-4483.1</v>
+        <v>-1589.04</v>
       </c>
       <c r="D142" t="n">
-        <v>-4483</v>
+        <v>-1589</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>PT513880151</t>
+          <t>MT18726720</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3008</t>
+          <t xml:space="preserve">              2105</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
         <is>
-          <t>JetUp, Lda.</t>
+          <t>ZuluWaves Limited</t>
         </is>
       </c>
       <c r="C143" t="n">
-        <v>-920</v>
+        <v>-2410.24</v>
       </c>
       <c r="D143" t="n">
-        <v>-920</v>
+        <v>-2410</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>PT518498298</t>
+          <t>MT30851503</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1031</t>
+          <t xml:space="preserve">              3110</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
+          <t>Arion Retail Group Poland Sp. z o.o.</t>
         </is>
       </c>
       <c r="C144" t="n">
-        <v>-1041.34</v>
+        <v>-18</v>
       </c>
       <c r="D144" t="n">
-        <v>-1041</v>
+        <v>-18</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>PT502635770</t>
+          <t>PL5253064487</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Poland</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2133</t>
+          <t xml:space="preserve">               679</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
         <is>
-          <t>Tulipa Mensageira LDA</t>
+          <t>Afonso Ferreira Faria unipessoal LDa</t>
         </is>
       </c>
       <c r="C145" t="n">
-        <v>-3732.06</v>
+        <v>-4531.1</v>
       </c>
       <c r="D145" t="n">
-        <v>-3732</v>
+        <v>-4531</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
-          <t>PT517035863</t>
+          <t>PT513880151</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
@@ -4483,303 +4483,303 @@
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3109</t>
+          <t xml:space="preserve">              3008</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
         <is>
-          <t>Arion Retail Group Romania S.R.L.</t>
+          <t>JetUp, Lda.</t>
         </is>
       </c>
       <c r="C146" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>-1383</v>
       </c>
       <c r="D146" t="n">
-        <v>0</v>
+        <v>-1383</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
-          <t>RO52745394</t>
+          <t>PT518498298</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2097</t>
+          <t xml:space="preserve">              1031</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>JET ADVISOR</t>
+          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
         </is>
       </c>
       <c r="C147" t="n">
-        <v>-268.3</v>
+        <v>-1302.34</v>
       </c>
       <c r="D147" t="n">
-        <v>-268</v>
+        <v>-1302</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>RO28308419</t>
+          <t>PT502635770</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1577</t>
+          <t xml:space="preserve">              2133</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>S.C. TOYO AVIATION S.R.L.</t>
+          <t>Tulipa Mensageira LDA</t>
         </is>
       </c>
       <c r="C148" t="n">
-        <v>-2950.35</v>
+        <v>-3732.06</v>
       </c>
       <c r="D148" t="n">
-        <v>-2950</v>
+        <v>-3732</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
-          <t>RO21977513</t>
+          <t>PT517035863</t>
         </is>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t xml:space="preserve">               420</t>
+          <t xml:space="preserve">              3109</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Zumaia Offshore, S.L.</t>
+          <t>Arion Retail Group Romania S.R.L.</t>
         </is>
       </c>
       <c r="C149" t="n">
-        <v>-1529.27</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="D149" t="n">
-        <v>-1529</v>
+        <v>0</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
-          <t>ESB95442182</t>
+          <t>RO52745394</t>
         </is>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>SPAIN</t>
+          <t>Romania</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t xml:space="preserve">               909</t>
+          <t xml:space="preserve">              2097</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>ERZOFF-SHORE, S.L.</t>
+          <t>JET ADVISOR</t>
         </is>
       </c>
       <c r="C150" t="n">
-        <v>-83.71000000000001</v>
+        <v>-268.3</v>
       </c>
       <c r="D150" t="n">
-        <v>-84</v>
+        <v>-268</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>ESB06919351</t>
+          <t>RO28308419</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Romania</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2236</t>
+          <t xml:space="preserve">              1577</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Espana Rope Access Solutions SL</t>
+          <t>S.C. TOYO AVIATION S.R.L.</t>
         </is>
       </c>
       <c r="C151" t="n">
-        <v>-2593.03</v>
+        <v>-2950.35</v>
       </c>
       <c r="D151" t="n">
-        <v>-2593</v>
+        <v>-2950</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>ESB09880675</t>
+          <t>RO21977513</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Romania</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2389</t>
+          <t xml:space="preserve">               420</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Geoxyz Spain SL</t>
+          <t>Zumaia Offshore, S.L.</t>
         </is>
       </c>
       <c r="C152" t="n">
-        <v>-218.34</v>
+        <v>-1529.27</v>
       </c>
       <c r="D152" t="n">
-        <v>-218</v>
+        <v>-1529</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>ESB13905591</t>
+          <t>ESB95442182</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>SPAIN</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2471</t>
+          <t xml:space="preserve">               909</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>C Survey</t>
+          <t>ERZOFF-SHORE, S.L.</t>
         </is>
       </c>
       <c r="C153" t="n">
-        <v>-529.09</v>
+        <v>-83.71000000000001</v>
       </c>
       <c r="D153" t="n">
-        <v>-529</v>
+        <v>-84</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>SE556782721601</t>
+          <t>ESB06919351</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2670</t>
+          <t xml:space="preserve">              2236</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Fjordtank Rederi AB</t>
+          <t>Espana Rope Access Solutions SL</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>-551.21</v>
+        <v>-2593.03</v>
       </c>
       <c r="D154" t="n">
-        <v>-551</v>
+        <v>-2593</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>SE556633100401</t>
+          <t>ESB09880675</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3135</t>
+          <t xml:space="preserve">              2389</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>FureBear AB</t>
+          <t>Geoxyz Spain SL</t>
         </is>
       </c>
       <c r="C155" t="n">
-        <v>-30</v>
+        <v>-218.34</v>
       </c>
       <c r="D155" t="n">
-        <v>-30</v>
+        <v>-218</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>SE559389323201</t>
+          <t>ESB13905591</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3133</t>
+          <t xml:space="preserve">              2471</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Furetank Rederi AB</t>
+          <t>C Survey</t>
         </is>
       </c>
       <c r="C156" t="n">
-        <v>-316.69</v>
+        <v>-529.09</v>
       </c>
       <c r="D156" t="n">
-        <v>-317</v>
+        <v>-529</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>SE556371751001</t>
+          <t>SE556782721601</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -4791,23 +4791,23 @@
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2692</t>
+          <t xml:space="preserve">              2670</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>HF Interior AB</t>
+          <t>Fjordtank Rederi AB</t>
         </is>
       </c>
       <c r="C157" t="n">
-        <v>-559.29</v>
+        <v>-551.21</v>
       </c>
       <c r="D157" t="n">
-        <v>-559</v>
+        <v>-551</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>SE556844774101</t>
+          <t>SE556633100401</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -4819,23 +4819,23 @@
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t xml:space="preserve">               725</t>
+          <t xml:space="preserve">              3135</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Linnea Shipping A/S</t>
+          <t>FureBear AB</t>
         </is>
       </c>
       <c r="C158" t="n">
-        <v>-2777.19</v>
+        <v>-30</v>
       </c>
       <c r="D158" t="n">
-        <v>-2777</v>
+        <v>-30</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>SE556405820301</t>
+          <t>SE559389323201</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -4847,23 +4847,23 @@
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2470</t>
+          <t xml:space="preserve">              3133</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Manta Systems AB</t>
+          <t>Furetank Rederi AB</t>
         </is>
       </c>
       <c r="C159" t="n">
-        <v>-348.08</v>
+        <v>-316.69</v>
       </c>
       <c r="D159" t="n">
-        <v>-348</v>
+        <v>-317</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>SE559457660401</t>
+          <t>SE556371751001</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -4875,23 +4875,23 @@
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t xml:space="preserve">               616</t>
+          <t xml:space="preserve">              2692</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>OljOla Shipping AB</t>
+          <t>HF Interior AB</t>
         </is>
       </c>
       <c r="C160" t="n">
-        <v>-339.67</v>
+        <v>-559.29</v>
       </c>
       <c r="D160" t="n">
-        <v>-340</v>
+        <v>-559</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>SE559151957301</t>
+          <t>SE556844774101</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -4903,23 +4903,23 @@
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1437</t>
+          <t xml:space="preserve">               725</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Q Workforce</t>
+          <t>Linnea Shipping A/S</t>
         </is>
       </c>
       <c r="C161" t="n">
-        <v>-921.9</v>
+        <v>-2777.19</v>
       </c>
       <c r="D161" t="n">
-        <v>-922</v>
+        <v>-2777</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>SE559200270201</t>
+          <t>SE556405820301</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -4931,23 +4931,23 @@
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1075</t>
+          <t xml:space="preserve">              2470</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Rederi AB Donsötank - EUR</t>
+          <t>Manta Systems AB</t>
         </is>
       </c>
       <c r="C162" t="n">
-        <v>-4743.49</v>
+        <v>-348.08</v>
       </c>
       <c r="D162" t="n">
-        <v>-4743</v>
+        <v>-348</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>SE556058292501</t>
+          <t>SE559457660401</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -4959,23 +4959,23 @@
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2735</t>
+          <t xml:space="preserve">               616</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Sirius Agency</t>
+          <t>OljOla Shipping AB</t>
         </is>
       </c>
       <c r="C163" t="n">
-        <v>50</v>
+        <v>-339.67</v>
       </c>
       <c r="D163" t="n">
-        <v>50</v>
+        <v>-340</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>SE556043575101</t>
+          <t>SE559151957301</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -4987,23 +4987,23 @@
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1655</t>
+          <t xml:space="preserve">              1437</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Sirius Shipping</t>
+          <t>Q Workforce</t>
         </is>
       </c>
       <c r="C164" t="n">
-        <v>-7409.64</v>
+        <v>-921.9</v>
       </c>
       <c r="D164" t="n">
-        <v>-7410</v>
+        <v>-922</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>SE556772536001</t>
+          <t>SE559200270201</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -5015,23 +5015,23 @@
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t xml:space="preserve">               962</t>
+          <t xml:space="preserve">              1075</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>VERITAS MANAGEMENT AB</t>
+          <t>Rederi AB Donsötank - EUR</t>
         </is>
       </c>
       <c r="C165" t="n">
-        <v>-2667.02</v>
+        <v>-4743.49</v>
       </c>
       <c r="D165" t="n">
-        <v>-2667</v>
+        <v>-4743</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>SE559003939101</t>
+          <t>SE556058292501</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -5043,26 +5043,110 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
+          <t xml:space="preserve">              2735</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Sirius Agency</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>50</v>
+      </c>
+      <c r="D166" t="n">
+        <v>50</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SE556043575101</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1655</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sirius Shipping</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>-7556.64</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-7557</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SE556772536001</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               962</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VERITAS MANAGEMENT AB</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>-2697.02</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-2697</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>SE559003939101</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t xml:space="preserve">              2580</t>
         </is>
       </c>
-      <c r="B166" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>West Atlantic Sweden AB</t>
         </is>
       </c>
-      <c r="C166" t="n">
+      <c r="C169" t="n">
         <v>-2523.14</v>
       </c>
-      <c r="D166" t="n">
+      <c r="D169" t="n">
         <v>-2523</v>
       </c>
-      <c r="E166" t="inlineStr">
+      <c r="E169" t="inlineStr">
         <is>
           <t>SE556062442001</t>
         </is>
       </c>
-      <c r="F166" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>

--- a/output/ICP Q2'26.xlsx
+++ b/output/ICP Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F169"/>
+  <dimension ref="A1:F124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,23 +451,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2358</t>
+          <t xml:space="preserve">              2534</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>AXIS Aviation Austria GmbH</t>
+          <t>JetView GmbH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-49.8</v>
+        <v>-459.99</v>
       </c>
       <c r="D2" t="n">
-        <v>-50</v>
+        <v>-460</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATU78323306</t>
+          <t>ATU78020035</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -479,51 +479,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2534</t>
+          <t xml:space="preserve">              3114</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JetView GmbH</t>
+          <t>Arion Retail Group Belgium</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-785.48</v>
+        <v>-30</v>
       </c>
       <c r="D3" t="n">
-        <v>-785</v>
+        <v>-30</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ATU78020035</t>
+          <t>BE1014587039</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Austria</t>
+          <t>Belgium</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3114</t>
+          <t xml:space="preserve">               883</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Arion Retail Group Belgium</t>
+          <t>Fugro Belgium BV</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-30</v>
+        <v>-1541</v>
       </c>
       <c r="D4" t="n">
-        <v>-30</v>
+        <v>-1541</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BE1014587039</t>
+          <t>BE0403026288</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -535,23 +535,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">               883</t>
+          <t xml:space="preserve">               493</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Fugro Belgium BV</t>
+          <t>GEOxyz bvba</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-1541</v>
+        <v>-149.24</v>
       </c>
       <c r="D5" t="n">
-        <v>-1541</v>
+        <v>-149</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BE0403026288</t>
+          <t>BE0465233774</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -563,23 +563,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">               493</t>
+          <t xml:space="preserve">               596</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GEOxyz bvba</t>
+          <t>Geo Aqua bvba</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-5188.39</v>
+        <v>-94.25</v>
       </c>
       <c r="D6" t="n">
-        <v>-5188</v>
+        <v>-94</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BE0465233774</t>
+          <t>BE0890302622</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">               596</t>
+          <t xml:space="preserve">               237</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Geo Aqua bvba</t>
+          <t>International Food Services NV</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-1604.84</v>
+        <v>-409.74</v>
       </c>
       <c r="D7" t="n">
-        <v>-1605</v>
+        <v>-410</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BE0890302622</t>
+          <t>BE0472409202</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -619,23 +619,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">               237</t>
+          <t xml:space="preserve">              2968</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>International Food Services NV</t>
+          <t>Subsea Global Solutions Belgium BV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-1689.57</v>
+        <v>-750</v>
       </c>
       <c r="D8" t="n">
-        <v>-1690</v>
+        <v>-750</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BE0472409202</t>
+          <t>BE0502793758</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -647,79 +647,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3070</t>
+          <t xml:space="preserve">              2920</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Seasoils (Enviros)</t>
+          <t>Dark Waves Ltd</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-187.8</v>
+        <v>-534</v>
       </c>
       <c r="D9" t="n">
-        <v>-188</v>
+        <v>-534</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BE0515949235</t>
+          <t>BG207801369</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2968</t>
+          <t xml:space="preserve">              2652</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Subsea Global Solutions Belgium BV</t>
+          <t>Hit Tourism LTD</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-750</v>
+        <v>-772.45</v>
       </c>
       <c r="D10" t="n">
-        <v>-750</v>
+        <v>-772</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BE0502793758</t>
+          <t>BG103594726</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2920</t>
+          <t xml:space="preserve">              2918</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Dark Waves Ltd</t>
+          <t>windshipping</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-1964.04</v>
+        <v>-21</v>
       </c>
       <c r="D11" t="n">
-        <v>-1964</v>
+        <v>-21</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BG207801369</t>
+          <t>BG205047575</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -731,135 +731,135 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2652</t>
+          <t xml:space="preserve">              2404</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Hit Tourism LTD</t>
+          <t>Marine Air Split</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-13274.05</v>
+        <v>-795</v>
       </c>
       <c r="D12" t="n">
-        <v>-13274</v>
+        <v>-795</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>BG103594726</t>
+          <t>HR90789004458</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Croatia</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">               404</t>
+          <t xml:space="preserve">               136</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Visitship Ltd</t>
+          <t>Asia Marine Philippines</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-50</v>
+        <v>-9</v>
       </c>
       <c r="D13" t="n">
-        <v>-50</v>
+        <v>-9</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>BG204690910</t>
+          <t>CY10342881S</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2918</t>
+          <t xml:space="preserve">              1439</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>windshipping</t>
+          <t>Atlas Inexco CY Ltd.</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-4035.02</v>
+        <v>-237</v>
       </c>
       <c r="D14" t="n">
-        <v>-4035</v>
+        <v>-237</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>BG205047575</t>
+          <t>CY10342092N</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2404</t>
+          <t xml:space="preserve">              2807</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Marine Air Split</t>
+          <t>Caribbean Shipping Ltd</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-1255.77</v>
+        <v>-148</v>
       </c>
       <c r="D15" t="n">
-        <v>-1256</v>
+        <v>-148</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>HR90789004458</t>
+          <t>CY10303314V</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">               136</t>
+          <t xml:space="preserve">               658</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Asia Marine Philippines</t>
+          <t>Henley Travel LTD</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-12520.16</v>
+        <v>-167.56</v>
       </c>
       <c r="D16" t="n">
-        <v>-12520</v>
+        <v>-168</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CY10342881S</t>
+          <t>CY10110942W</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -871,23 +871,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1439</t>
+          <t xml:space="preserve">              1191</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Atlas Inexco CY Ltd.</t>
+          <t>IO Line Limited</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-390.36</v>
+        <v>-10</v>
       </c>
       <c r="D17" t="n">
-        <v>-390</v>
+        <v>-10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CY10342092N</t>
+          <t>CY10440516Z</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -899,23 +899,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">               488</t>
+          <t xml:space="preserve">              3117</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Cymare Shipmanagement Ltd</t>
+          <t>OSM SHIP MANAGEMENT CYPRUS LTD</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-200</v>
+        <v>-17.15</v>
       </c>
       <c r="D18" t="n">
-        <v>-200</v>
+        <v>-17</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CY10309832T</t>
+          <t>CY10377387I</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2809</t>
+          <t xml:space="preserve">              1210</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Eurica Shipping Ltd</t>
+          <t>Ocean Advice Ltd.</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-2495.29</v>
+        <v>-243</v>
       </c>
       <c r="D19" t="n">
-        <v>-2495</v>
+        <v>-243</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CY10303314V</t>
+          <t>CY10438212J</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -955,23 +955,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">               658</t>
+          <t xml:space="preserve">               375</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Henley Travel LTD</t>
+          <t>SMT SHIPPING (CYPRUS ) LTD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-6802.47</v>
+        <v>-1101.06</v>
       </c>
       <c r="D20" t="n">
-        <v>-6802</v>
+        <v>-1101</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CY10110942W</t>
+          <t>CY10039349U</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -983,23 +983,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1191</t>
+          <t xml:space="preserve">               204</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>IO Line Limited</t>
+          <t>Scylla Gastro Ltd</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-56.8</v>
+        <v>-2760.21</v>
       </c>
       <c r="D21" t="n">
-        <v>-57</v>
+        <v>-2760</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CY10440516Z</t>
+          <t>CY10318112E</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1011,23 +1011,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1520</t>
+          <t xml:space="preserve">               498</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Lowland International Shipping Cyprus Ltd</t>
+          <t>Scylla Nautic Ltd</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-1566.14</v>
+        <v>-2002.81</v>
       </c>
       <c r="D22" t="n">
-        <v>-1566</v>
+        <v>-2003</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CY10252740F</t>
+          <t>CY10338093B</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1039,275 +1039,275 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2446</t>
+          <t xml:space="preserve">              1579</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>OPEN OCEAN SERVICES LTD</t>
+          <t>Cyan Renewables Aps</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-179.99</v>
+        <v>-250</v>
       </c>
       <c r="D23" t="n">
-        <v>-180</v>
+        <v>-250</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>CY60023930P</t>
+          <t>DK43887904</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3117</t>
+          <t xml:space="preserve">              1628</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>OSM SHIP MANAGEMENT CYPRUS LTD</t>
+          <t>Cyan Renewables ac1  Aps</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-1749.23</v>
+        <v>-494.76</v>
       </c>
       <c r="D24" t="n">
-        <v>-1749</v>
+        <v>-495</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>CY10377387I</t>
+          <t>DK43958496</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1210</t>
+          <t xml:space="preserve">              2901</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Ocean Advice Ltd.</t>
+          <t>ESVAGT A/S</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-1284.01</v>
+        <v>-974</v>
       </c>
       <c r="D25" t="n">
-        <v>-1284</v>
+        <v>-974</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>CY10438212J</t>
+          <t>DK60698813</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">               337</t>
+          <t xml:space="preserve">               667</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Reederei Nord Shipmanagement Ltd.</t>
+          <t>MHO Operations ApS</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-1171.65</v>
+        <v>-442.3</v>
       </c>
       <c r="D26" t="n">
-        <v>-1172</v>
+        <v>-442</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>CY10344686Z</t>
+          <t>DK38948563</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">               369</t>
+          <t xml:space="preserve">              2347</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SEACREW MANAGEMENT LTD</t>
+          <t>SHIP 103 ApS</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-1958.39</v>
+        <v>-89.53999999999999</v>
       </c>
       <c r="D27" t="n">
-        <v>-1958</v>
+        <v>-90</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>CY10205318D</t>
+          <t>DK40344446</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">               375</t>
+          <t xml:space="preserve">              1295</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>SMT SHIPPING (CYPRUS ) LTD</t>
+          <t>Ship 102 ApS</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-2567.3</v>
+        <v>-40</v>
       </c>
       <c r="D28" t="n">
-        <v>-2567</v>
+        <v>-40</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>CY10039349U</t>
+          <t>DK43303384</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">               204</t>
+          <t xml:space="preserve">              2348</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Scylla Gastro Ltd</t>
+          <t>Ship 104 ApS</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-35927.77</v>
+        <v>-107.92</v>
       </c>
       <c r="D29" t="n">
-        <v>-35928</v>
+        <v>-108</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>CY10318112E</t>
+          <t>DK44210096</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">               498</t>
+          <t xml:space="preserve">              2349</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Scylla Nautic Ltd</t>
+          <t>Ship 105 ApS</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-28485.84</v>
+        <v>-26.38</v>
       </c>
       <c r="D30" t="n">
-        <v>-28486</v>
+        <v>-26</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>CY10338093B</t>
+          <t>DK44210126</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2650</t>
+          <t xml:space="preserve">               123</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Unipolar Shipping Limited</t>
+          <t>TORM A/S</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-588.8</v>
+        <v>-29.83</v>
       </c>
       <c r="D31" t="n">
-        <v>-589</v>
+        <v>-30</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>CY60083461Z</t>
+          <t>DK22460218</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">               868</t>
+          <t xml:space="preserve">              1424</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>C-bed Holding A/S</t>
+          <t>Terntank Rederi A/S</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-85.5</v>
+        <v>-135.05</v>
       </c>
       <c r="D32" t="n">
-        <v>-86</v>
+        <v>-135</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DK37183555</t>
+          <t>DK34584362</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1319,863 +1319,863 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3056</t>
+          <t xml:space="preserve">               128</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Christiania Shipping A/S</t>
+          <t>Amisco AS</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-167</v>
+        <v>-1432</v>
       </c>
       <c r="D33" t="n">
-        <v>-167</v>
+        <v>-1432</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>DK40533516</t>
+          <t>EE100100240</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1579</t>
+          <t xml:space="preserve">              1524</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cyan Renewables Aps</t>
+          <t>Atrica-Marine OU</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-712.84</v>
+        <v>-22</v>
       </c>
       <c r="D34" t="n">
-        <v>-713</v>
+        <v>-22</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>DK43887904</t>
+          <t>EE100218912</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1628</t>
+          <t xml:space="preserve">              2267</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cyan Renewables ac1  Aps</t>
+          <t>FinMetalock</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-3597.96</v>
+        <v>-146</v>
       </c>
       <c r="D35" t="n">
-        <v>-3598</v>
+        <v>-146</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>DK43958496</t>
+          <t>EE101329758</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2901</t>
+          <t xml:space="preserve">               548</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>ESVAGT A/S</t>
+          <t>Klip Marine Shipmanagement Ltd</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-3569.81</v>
+        <v>-46</v>
       </c>
       <c r="D36" t="n">
-        <v>-3570</v>
+        <v>-46</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>DK60698813</t>
+          <t>EE101033617</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">               667</t>
+          <t xml:space="preserve">               986</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>MHO Operations ApS</t>
+          <t>OU VLM REPAIR</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-4357.16</v>
+        <v>-656</v>
       </c>
       <c r="D37" t="n">
-        <v>-4357</v>
+        <v>-656</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>DK38948563</t>
+          <t>EE101606918</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">               840</t>
+          <t xml:space="preserve">              2095</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ocean Zephyr ApS</t>
+          <t>Swaileap OÜ LSA</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-1270.86</v>
+        <v>-15</v>
       </c>
       <c r="D38" t="n">
-        <v>-1271</v>
+        <v>-15</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>DK41294574</t>
+          <t>EE102074617</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2347</t>
+          <t xml:space="preserve">              2310</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>SHIP 103 ApS</t>
+          <t>TS Shipping OÜ</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-702.9400000000001</v>
+        <v>-271</v>
       </c>
       <c r="D39" t="n">
-        <v>-703</v>
+        <v>-271</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>DK40344446</t>
+          <t>EE101597632</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1080</t>
+          <t xml:space="preserve">               391</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Ship 101 ApS</t>
+          <t>Tschudi Ship Management AS</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-164.82</v>
+        <v>-17</v>
       </c>
       <c r="D40" t="n">
-        <v>-165</v>
+        <v>-17</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>DK43303414</t>
+          <t>EE100708642</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1295</t>
+          <t xml:space="preserve">               206</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Ship 102 ApS</t>
+          <t>ESL Shipping Oy</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-804.0600000000001</v>
+        <v>-1295</v>
       </c>
       <c r="D41" t="n">
-        <v>-804</v>
+        <v>-1295</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>DK43303384</t>
+          <t>FI02011264</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2348</t>
+          <t xml:space="preserve">              3124</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ship 104 ApS</t>
+          <t>Oy AtoB@C Shipping Ab</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>-848.9200000000001</v>
+        <v>0</v>
       </c>
       <c r="D42" t="n">
-        <v>-849</v>
+        <v>0</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>DK44210096</t>
+          <t>FI25781405</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2349</t>
+          <t xml:space="preserve">               334</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ship 105 ApS</t>
+          <t>Rederi ab Nathalie</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-184.18</v>
+        <v>-117</v>
       </c>
       <c r="D43" t="n">
-        <v>-184</v>
+        <v>-117</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>DK44210126</t>
+          <t>FI22811672</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">               380</t>
+          <t xml:space="preserve">               965</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Svendborg Bugser A/S</t>
+          <t>COMPAGNIE DU PONANT</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-307.25</v>
+        <v>-2284</v>
       </c>
       <c r="D44" t="n">
-        <v>-307</v>
+        <v>-2284</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>DK21792802</t>
+          <t>FR83344497011</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">               123</t>
+          <t xml:space="preserve">               564</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>TORM A/S</t>
+          <t>GeoXYZ sarl</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-285.75</v>
+        <v>-20</v>
       </c>
       <c r="D45" t="n">
-        <v>-286</v>
+        <v>-20</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>DK22460218</t>
+          <t>FR90507902211</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1424</t>
+          <t xml:space="preserve">              2490</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Terntank Rederi A/S</t>
+          <t>PXGEO France SAS</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-6974.43</v>
+        <v>-700.28</v>
       </c>
       <c r="D46" t="n">
-        <v>-6974</v>
+        <v>-700</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>DK34584362</t>
+          <t>FR70918328766</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">               128</t>
+          <t xml:space="preserve">               382</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Amisco AS</t>
+          <t>THENAMARIS SHIPS MANAGEMENT INC</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-4721.84</v>
+        <v>-656.14</v>
       </c>
       <c r="D47" t="n">
-        <v>-4722</v>
+        <v>-656</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EE100100240</t>
+          <t>EL098010844</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>GREECE</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1524</t>
+          <t xml:space="preserve">              2450</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Atrica-Marine OU</t>
+          <t>Air Partner International GmbH</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-1250.64</v>
+        <v>-92.99000000000001</v>
       </c>
       <c r="D48" t="n">
-        <v>-1251</v>
+        <v>-93</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>EE100218912</t>
+          <t>DE184629207</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2267</t>
+          <t xml:space="preserve">               152</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>FinMetalock</t>
+          <t>Axxaz Europe GmbH</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-1709.78</v>
+        <v>-773</v>
       </c>
       <c r="D49" t="n">
-        <v>-1710</v>
+        <v>-773</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>EE101329758</t>
+          <t>DE296988120</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2798</t>
+          <t xml:space="preserve">              2736</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>HFH Grupp OÜ</t>
+          <t>Beteiligungsgesellschaft MS Santa Vanessa mbH &amp; Co</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-325</v>
+        <v>-23</v>
       </c>
       <c r="D50" t="n">
-        <v>-325</v>
+        <v>-23</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>EE101584289</t>
+          <t>DE232610165</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">               548</t>
+          <t xml:space="preserve">              2319</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Klip Marine Shipmanagement Ltd</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-653.11</v>
+        <v>-85</v>
       </c>
       <c r="D51" t="n">
-        <v>-653</v>
+        <v>-85</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>EE101033617</t>
+          <t>DE249771948</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">               986</t>
+          <t xml:space="preserve">              2318</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>OU VLM REPAIR</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-3310.88</v>
+        <v>-42</v>
       </c>
       <c r="D52" t="n">
-        <v>-3311</v>
+        <v>-42</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>EE101606918</t>
+          <t>DE213881581</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2095</t>
+          <t xml:space="preserve">              2107</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Swaileap OÜ LSA</t>
+          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-6278.9</v>
+        <v>-745</v>
       </c>
       <c r="D53" t="n">
-        <v>-6279</v>
+        <v>-745</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>EE102074617</t>
+          <t>DE293561563</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2310</t>
+          <t xml:space="preserve">              1169</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>TS Shipping OÜ</t>
+          <t>EMS Crewing GmbH</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-617.74</v>
+        <v>-26</v>
       </c>
       <c r="D54" t="n">
-        <v>-618</v>
+        <v>-26</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>EE101597632</t>
+          <t>DE262060886</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">               391</t>
+          <t xml:space="preserve">              2284</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Tschudi Ship Management AS</t>
+          <t>Hansa Safety Services GmbH</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-1149.14</v>
+        <v>-663.23</v>
       </c>
       <c r="D55" t="n">
-        <v>-1149</v>
+        <v>-663</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>EE100708642</t>
+          <t>DE284814823</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">               206</t>
+          <t xml:space="preserve">              2016</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ESL Shipping Oy</t>
+          <t>KG MS CPO BARCELONA Offen Reederei UG (haftungsbes</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-7939.44</v>
+        <v>-108</v>
       </c>
       <c r="D56" t="n">
-        <v>-7939</v>
+        <v>-108</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>FI02011264</t>
+          <t>DE298771680</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3124</t>
+          <t xml:space="preserve">              2376</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Oy AtoB@C Shipping Ab</t>
+          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>2.664535259100376e-15</v>
+        <v>-21</v>
       </c>
       <c r="D57" t="n">
-        <v>0</v>
+        <v>-21</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>FI25781405</t>
+          <t>DE257260686</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">               334</t>
+          <t xml:space="preserve">              2684</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Rederi ab Nathalie</t>
+          <t>Martide Holding GmbH</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-2854.89</v>
+        <v>-50</v>
       </c>
       <c r="D58" t="n">
-        <v>-2855</v>
+        <v>-50</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>FI22811672</t>
+          <t>DE450210277</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">               965</t>
+          <t xml:space="preserve">               309</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>COMPAGNIE DU PONANT</t>
+          <t>NSB Crewing Solutions</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-2274.5</v>
+        <v>-15</v>
       </c>
       <c r="D59" t="n">
-        <v>-2274</v>
+        <v>-15</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>FR83344497011</t>
+          <t>DE283269969</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">               564</t>
+          <t xml:space="preserve">               310</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>GeoXYZ sarl</t>
+          <t>NSB Reederei GmbH &amp; Co. Kg</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-446.08</v>
+        <v>-93.2</v>
       </c>
       <c r="D60" t="n">
-        <v>-446</v>
+        <v>-93</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>FR90507902211</t>
+          <t>DE116474094</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2490</t>
+          <t xml:space="preserve">              2238</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>PXGEO France SAS</t>
+          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-1437.91</v>
+        <v>-21</v>
       </c>
       <c r="D61" t="n">
-        <v>-1438</v>
+        <v>-21</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>FR70918328766</t>
+          <t>DE362363142</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">               382</t>
+          <t xml:space="preserve">               298</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>THENAMARIS SHIPS MANAGEMENT INC</t>
+          <t>Nordic Hamburg Crewing Services GmbH</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-22</v>
+        <v>-1878</v>
       </c>
       <c r="D62" t="n">
-        <v>-22</v>
+        <v>-1878</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>EL098010844</t>
+          <t>DE309948810</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>GREECE</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">               945</t>
+          <t xml:space="preserve">              2678</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>AMARO Travel GmbH</t>
+          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-53.6</v>
+        <v>-1631.97</v>
       </c>
       <c r="D63" t="n">
-        <v>-54</v>
+        <v>-1632</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DE309139121</t>
+          <t>DE285660591</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2187,23 +2187,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2450</t>
+          <t xml:space="preserve">              3064</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Air Partner International GmbH</t>
+          <t>OBC by Avico GmbH</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-672.04</v>
+        <v>-72.99000000000001</v>
       </c>
       <c r="D64" t="n">
-        <v>-672</v>
+        <v>-73</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DE184629207</t>
+          <t>DE457137561</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2215,23 +2215,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1576</t>
+          <t xml:space="preserve">              1498</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Andreas Zerr</t>
+          <t>Reederei F. Laeisz GmbH</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-173.2</v>
+        <v>-84</v>
       </c>
       <c r="D65" t="n">
-        <v>-173</v>
+        <v>-84</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DE221230922</t>
+          <t>DE811585869</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2243,23 +2243,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">               152</t>
+          <t xml:space="preserve">              3017</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Axxaz Europe GmbH</t>
+          <t>SUNDAIR Gmbh</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-19230.99</v>
+        <v>-192</v>
       </c>
       <c r="D66" t="n">
-        <v>-19231</v>
+        <v>-192</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DE296988120</t>
+          <t>DE305307186</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2271,23 +2271,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2736</t>
+          <t xml:space="preserve">              3026</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Beteiligungsgesellschaft MS Santa Vanessa mbH &amp; Co</t>
+          <t>T &amp; T In Situ Machining GmbH</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-23</v>
+        <v>-543.9400000000001</v>
       </c>
       <c r="D67" t="n">
-        <v>-23</v>
+        <v>-544</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DE232610165</t>
+          <t>DE327579122</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2299,23 +2299,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2319</t>
+          <t xml:space="preserve">               832</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
+          <t>UHL Chartering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-85</v>
+        <v>-436.86</v>
       </c>
       <c r="D68" t="n">
-        <v>-85</v>
+        <v>-437</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DE249771948</t>
+          <t>DE350330837</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2327,23 +2327,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2318</t>
+          <t xml:space="preserve">              1065</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
+          <t>UHL Crewing GmbH</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-42</v>
+        <v>-983</v>
       </c>
       <c r="D69" t="n">
-        <v>-42</v>
+        <v>-983</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DE213881581</t>
+          <t>DE330510394</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2355,23 +2355,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2594</t>
+          <t xml:space="preserve">               396</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG forRDO Endeavour - 2522</t>
+          <t>USC Crew GmbH</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-196.47</v>
+        <v>-140.72</v>
       </c>
       <c r="D70" t="n">
-        <v>-196</v>
+        <v>-141</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DE307865976</t>
+          <t>DE274971782</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2383,23 +2383,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2107</t>
+          <t xml:space="preserve">              3065</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
+          <t>USC GmbH</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-2683.32</v>
+        <v>-256.19</v>
       </c>
       <c r="D71" t="n">
-        <v>-2683</v>
+        <v>-256</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DE293561563</t>
+          <t>DE334043640</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2411,23 +2411,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">               197</t>
+          <t xml:space="preserve">               395</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>DS Crewing Sevices GmbH</t>
+          <t>United Engineering Solutions GmbH</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="D72" t="n">
-        <v>-30</v>
+        <v>0</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DE318346366</t>
+          <t>DE319531170</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2439,23 +2439,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1553</t>
+          <t xml:space="preserve">               867</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Davit-Company GmbH &amp; W. Harms</t>
+          <t>United Heavy Lift GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-96.31999999999999</v>
+        <v>-473</v>
       </c>
       <c r="D73" t="n">
-        <v>-96</v>
+        <v>-473</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DE291870147</t>
+          <t>DE350330845</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2467,23 +2467,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1169</t>
+          <t xml:space="preserve">               637</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>EMS Crewing GmbH</t>
+          <t>over-C Crewing GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-146</v>
+        <v>-14</v>
       </c>
       <c r="D74" t="n">
-        <v>-146</v>
+        <v>-14</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DE262060886</t>
+          <t>DE321517652</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2495,2658 +2495,1398 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2452</t>
+          <t xml:space="preserve">              3108</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>F.Laeisz GmbH Hamburg</t>
+          <t>Arion Greece S.A.</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>-53.6</v>
+        <v>0</v>
       </c>
       <c r="D75" t="n">
-        <v>-54</v>
+        <v>0</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>DE170925486</t>
+          <t>EL803103395</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">               231</t>
+          <t xml:space="preserve">               155</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GP Care Solutions GmbH</t>
+          <t>BLUE PLANET SHIPPING LTD</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-1540.93</v>
+        <v>-15</v>
       </c>
       <c r="D76" t="n">
-        <v>-1541</v>
+        <v>-15</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>DE322179714</t>
+          <t>EL098093842</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">               601</t>
+          <t xml:space="preserve">               966</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GoodCrew GmbH</t>
+          <t>GIOVANTI TRAVEL S. A. MARKOU HOTEL AND TOURIST COM</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-2664.29</v>
+        <v>-30</v>
       </c>
       <c r="D77" t="n">
-        <v>-2664</v>
+        <v>-30</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>DE326784905</t>
+          <t>EL095223487</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2284</t>
+          <t xml:space="preserve">              2315</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Hansa Safety Services GmbH</t>
+          <t>Marathon Airlines SA</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-1085.05</v>
+        <v>-212.08</v>
       </c>
       <c r="D78" t="n">
-        <v>-1085</v>
+        <v>-212</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>DE284814823</t>
+          <t>EL800894668</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1146</t>
+          <t xml:space="preserve">              1058</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>KG MS 2. CPO Livorno Offen Reederei GmbH &amp; Co. c/o</t>
+          <t>Power Sub Link SA</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-25</v>
+        <v>-106</v>
       </c>
       <c r="D79" t="n">
-        <v>-25</v>
+        <v>-106</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>DE322053391</t>
+          <t>EL800357365</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1145</t>
+          <t xml:space="preserve">              2103</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>KG MS CPO LA SPEZIA Offen Reederei UG (haftungsbes</t>
+          <t>ROKS MARITIME INC</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-383</v>
+        <v>-42.4</v>
       </c>
       <c r="D80" t="n">
-        <v>-383</v>
+        <v>-42</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>DE298771680</t>
+          <t>EL996795284</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2376</t>
+          <t xml:space="preserve">               343</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
+          <t>Roxana Shipping S.A.</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>-46</v>
+        <v>228</v>
       </c>
       <c r="D81" t="n">
-        <v>-46</v>
+        <v>228</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>DE257260686</t>
+          <t>EL098093983</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1144</t>
+          <t xml:space="preserve">              2295</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>KG MS CPO VENEZIA Offen Reederei GmbH &amp; Co. c/o CP</t>
+          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-186.61</v>
+        <v>-428.12</v>
       </c>
       <c r="D82" t="n">
-        <v>-187</v>
+        <v>-428</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>DE256596537</t>
+          <t>EL801158466</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2015</t>
+          <t xml:space="preserve">               896</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>KG MS Santa Viola Offen Reederei GmbH &amp; Co. c/o CP</t>
+          <t>SRS WHOLESALE (RE)INSURANCE BROKERS A.E.</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-25</v>
+        <v>-1276.96</v>
       </c>
       <c r="D83" t="n">
-        <v>-25</v>
+        <v>-1277</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>DE230140293</t>
+          <t>EL801153262</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1435</t>
+          <t xml:space="preserve">              2655</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>M2L Pacific S.A.</t>
+          <t>THALPIS CRS SA</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-1596.11</v>
+        <v>-175.72</v>
       </c>
       <c r="D84" t="n">
-        <v>-1596</v>
+        <v>-176</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>DE811585869</t>
+          <t>EL996435463</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1916</t>
+          <t xml:space="preserve">              2924</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>MS "Paganella 2" GmbH &amp; Co. KG</t>
+          <t>THENAMARIS CONBULK INC.</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-26.8</v>
+        <v>-21</v>
       </c>
       <c r="D85" t="n">
-        <v>-27</v>
+        <v>-21</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>DE292632581</t>
+          <t>EL996795087</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1856</t>
+          <t xml:space="preserve">              2923</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>MS "Pagna" GmbH &amp; Co. KG</t>
+          <t>Thenamaris LNG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-75</v>
+        <v>-176.3</v>
       </c>
       <c r="D86" t="n">
-        <v>-75</v>
+        <v>-176</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>DE261459100</t>
+          <t>EL997596883</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1548</t>
+          <t xml:space="preserve">              3021</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>MS "PolarPacific" GmbH &amp; Co. KG</t>
+          <t>Velos Tankers Ltd.</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-260.01</v>
+        <v>-9.99</v>
       </c>
       <c r="D87" t="n">
-        <v>-260</v>
+        <v>-10</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>DE275633887</t>
+          <t>EL996864325</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2859</t>
+          <t xml:space="preserve">              3111</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>MS BSG Bimini GmbH &amp; Co.KG  c/o CPO Crewing GmbH &amp;</t>
+          <t>Arion Retail Group Hungary KFT</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-25</v>
+        <v>-19.98</v>
       </c>
       <c r="D88" t="n">
-        <v>-25</v>
+        <v>-20</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>DE346013071</t>
+          <t>HU32887413</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2684</t>
+          <t xml:space="preserve">              1952</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Martide Holding GmbH</t>
+          <t>Fleet Air International Kft.</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>16.52</v>
+        <v>-390.83</v>
       </c>
       <c r="D89" t="n">
-        <v>17</v>
+        <v>-391</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>DE450210277</t>
+          <t>HU13819822</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">               309</t>
+          <t xml:space="preserve">              2927</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>NSB Crewing Solutions</t>
+          <t>FLY4 Airlines Green Limited</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-4881.02</v>
+        <v>-3959.11</v>
       </c>
       <c r="D90" t="n">
-        <v>-4881</v>
+        <v>-3959</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>DE283269969</t>
+          <t>IE4197556QH</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">               310</t>
+          <t xml:space="preserve">               319</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>NSB Reederei GmbH &amp; Co. Kg</t>
+          <t>Pacific Blue Ltd</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-843.41</v>
+        <v>-92.59999999999999</v>
       </c>
       <c r="D91" t="n">
-        <v>-843</v>
+        <v>-93</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>DE116474094</t>
+          <t>IE6333494O</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2238</t>
+          <t xml:space="preserve">              2040</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
+          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-121.4</v>
+        <v>-253</v>
       </c>
       <c r="D92" t="n">
-        <v>-121</v>
+        <v>-253</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>DE362363142</t>
+          <t>IT02122640994</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">               298</t>
+          <t xml:space="preserve">                85</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Nordic Hamburg Crewing Services GmbH</t>
+          <t>Crewplanet SIA</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-31386</v>
+        <v>-24707.61</v>
       </c>
       <c r="D93" t="n">
-        <v>-31386</v>
+        <v>-24708</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>DE309948810</t>
+          <t>LV40003789592</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2678</t>
+          <t xml:space="preserve">               340</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
+          <t>RIX Shipmanagement LTD</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-2397.4</v>
+        <v>-5</v>
       </c>
       <c r="D94" t="n">
-        <v>-2397</v>
+        <v>-5</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>DE285660591</t>
+          <t>LV40103681236</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3088</t>
+          <t xml:space="preserve">              2420</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Nordic Tokyo GmbH &amp; Co. KG c/o Nordic Cruise Manag</t>
+          <t>SIA OJ Travel</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-182.4</v>
+        <v>-142.9</v>
       </c>
       <c r="D95" t="n">
-        <v>-182</v>
+        <v>-143</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>DE451301791</t>
+          <t>LV40003286572</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3064</t>
+          <t xml:space="preserve">              1091</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>OBC by Avico GmbH</t>
+          <t>UNION AVIATION AS</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-573.39</v>
+        <v>-65.40000000000001</v>
       </c>
       <c r="D96" t="n">
-        <v>-573</v>
+        <v>-65</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>DE457137561</t>
+          <t>LV40203294676</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3017</t>
+          <t xml:space="preserve">              2742</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>SUNDAIR Gmbh</t>
+          <t>BALTNAUTIC SHIPPING LTD</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-192</v>
+        <v>-205.49</v>
       </c>
       <c r="D97" t="n">
-        <v>-192</v>
+        <v>-205</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>DE305307186</t>
+          <t>LT417071917</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Lithuania</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">               496</t>
+          <t xml:space="preserve">               569</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Scheibert &amp; Meissner Personalberatung GbR</t>
+          <t>GEO@SEA Luxembourg S.A.</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-75</v>
+        <v>-224.26</v>
       </c>
       <c r="D98" t="n">
-        <v>-75</v>
+        <v>-224</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>DE240712065</t>
+          <t>LU32235384</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Luxembourg</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3026</t>
+          <t xml:space="preserve">               862</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>T &amp; T In Situ Machining GmbH</t>
+          <t>Atlantis Tankers Group (Malta) Ltd.</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-543.9400000000001</v>
+        <v>-5</v>
       </c>
       <c r="D99" t="n">
-        <v>-544</v>
+        <v>-5</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>DE327579122</t>
+          <t>MT21829715</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">               832</t>
+          <t xml:space="preserve">              1465</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>UHL Chartering GmbH &amp; Co. KG</t>
+          <t>CldN Malta Ltd.</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-1446.3</v>
+        <v>-668</v>
       </c>
       <c r="D100" t="n">
-        <v>-1446</v>
+        <v>-668</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>DE350330837</t>
+          <t>MT22140026</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1065</t>
+          <t xml:space="preserve">              2194</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>UHL Crewing GmbH</t>
+          <t>Elit’Avia Malta Ltd</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-5623.64</v>
+        <v>-9.99</v>
       </c>
       <c r="D101" t="n">
-        <v>-5624</v>
+        <v>-10</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>DE330510394</t>
+          <t>MT19960414</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">               396</t>
+          <t xml:space="preserve">               218</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>USC Crew GmbH</t>
+          <t>FT Portoria Tankers Ltd</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-10792.82</v>
+        <v>-20</v>
       </c>
       <c r="D102" t="n">
-        <v>-10793</v>
+        <v>-20</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>DE274971782</t>
+          <t>MT22398518</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3065</t>
+          <t xml:space="preserve">               718</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>USC GmbH</t>
+          <t>Furtrans Tanker Holdings Ltd</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-2638.95</v>
+        <v>-646.3499999999999</v>
       </c>
       <c r="D103" t="n">
-        <v>-2639</v>
+        <v>-646</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>DE334043640</t>
+          <t>MT26731101</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">               397</t>
+          <t xml:space="preserve">              2408</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>UVIS UG (haftungsbeschraenkt)</t>
+          <t>Hans Travel Ltd</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>-1187.48</v>
+        <v>250</v>
       </c>
       <c r="D104" t="n">
-        <v>-1187</v>
+        <v>250</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>DE319612386</t>
+          <t>MT28450014</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">               395</t>
+          <t xml:space="preserve">              2939</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>United Engineering Solutions GmbH</t>
+          <t>Lighthouse Yachting Malta Limited</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>24</v>
+        <v>-17.22</v>
       </c>
       <c r="D105" t="n">
-        <v>24</v>
+        <v>-17</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>DE319531170</t>
+          <t>MT29674336</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">               867</t>
+          <t xml:space="preserve">              2037</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>United Heavy Lift GmbH &amp; Co. KG</t>
+          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-1667.09</v>
+        <v>-313.99</v>
       </c>
       <c r="D106" t="n">
-        <v>-1667</v>
+        <v>-314</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>DE350330845</t>
+          <t>MT27270636</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">               637</t>
+          <t xml:space="preserve">              2036</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>over-C Crewing GmbH &amp; Co. KG</t>
+          <t>Quinto Tankers Ltd</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-1203.67</v>
+        <v>-36.28</v>
       </c>
       <c r="D107" t="n">
-        <v>-1204</v>
+        <v>-36</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>DE321517652</t>
+          <t>MT27591013</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2295</t>
+          <t xml:space="preserve">              2105</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
+          <t>ZuluWaves Limited</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-281</v>
+        <v>-108.6</v>
       </c>
       <c r="D108" t="n">
-        <v>-281</v>
+        <v>-109</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>EL801158466</t>
+          <t>MT30851503</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Malta</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">               896</t>
+          <t xml:space="preserve">               679</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>SRS WHOLESALE (RE)INSURANCE BROKERS A.E.</t>
+          <t>Afonso Ferreira Faria unipessoal LDa</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-264</v>
+        <v>-1874.48</v>
       </c>
       <c r="D109" t="n">
-        <v>-264</v>
+        <v>-1874</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>EL801153262</t>
+          <t>PT513880151</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2655</t>
+          <t xml:space="preserve">              3008</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>THALPIS CRS SA</t>
+          <t>JetUp, Lda.</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-117.69</v>
+        <v>-704</v>
       </c>
       <c r="D110" t="n">
-        <v>-118</v>
+        <v>-704</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>EL996435463</t>
+          <t>PT518498298</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3111</t>
+          <t xml:space="preserve">              1031</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Arion Retail Group Hungary KFT</t>
+          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-87.78</v>
+        <v>-862</v>
       </c>
       <c r="D111" t="n">
-        <v>-88</v>
+        <v>-862</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>HU32887413</t>
+          <t>PT502635770</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1952</t>
+          <t xml:space="preserve">              2133</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Fleet Air International Kft.</t>
+          <t>Tulipa Mensageira LDA</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>-2080.78</v>
+        <v>0</v>
       </c>
       <c r="D112" t="n">
-        <v>-2081</v>
+        <v>0</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>HU13819822</t>
+          <t>PT517035863</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Portugal</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2486</t>
+          <t xml:space="preserve">              3109</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Alpha Marine</t>
+          <t>Arion Retail Group Romania S.R.L.</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>-325.4</v>
+        <v>0</v>
       </c>
       <c r="D113" t="n">
-        <v>-325</v>
+        <v>0</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>IE3417853KH</t>
+          <t>RO52745394</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Romania</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2927</t>
+          <t xml:space="preserve">              1577</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>FLY4 Airlines Green Limited</t>
+          <t>S.C. TOYO AVIATION S.R.L.</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-18409.84</v>
+        <v>-51.2</v>
       </c>
       <c r="D114" t="n">
-        <v>-18410</v>
+        <v>-51</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>IE4197556QH</t>
+          <t>RO21977513</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Romania</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">               319</t>
+          <t xml:space="preserve">               420</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Pacific Blue Ltd</t>
+          <t>Zumaia Offshore, S.L.</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-5628.06</v>
+        <v>-111.68</v>
       </c>
       <c r="D115" t="n">
-        <v>-5628</v>
+        <v>-112</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>IE6333494O</t>
+          <t>ESB95442182</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>SPAIN</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2040</t>
+          <t xml:space="preserve">               909</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
+          <t>ERZOFF-SHORE, S.L.</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-581.6</v>
+        <v>-15.91</v>
       </c>
       <c r="D116" t="n">
-        <v>-582</v>
+        <v>-16</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>IT02122640994</t>
+          <t>ESB06919351</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Spain</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1529</t>
+          <t xml:space="preserve">              2471</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OMEGA S.R.L.</t>
+          <t>C Survey</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-47.75</v>
+        <v>-47.49</v>
       </c>
       <c r="D117" t="n">
-        <v>-48</v>
+        <v>-47</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>IT02343130270</t>
+          <t>SE556782721601</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">                34</t>
+          <t xml:space="preserve">               725</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>C Teleport AS</t>
+          <t>Linnea Shipping A/S</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-228283.32</v>
+        <v>-5</v>
       </c>
       <c r="D118" t="n">
-        <v>-228283</v>
+        <v>-5</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>LV40203039827</t>
+          <t>SE556405820301</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">                85</t>
+          <t xml:space="preserve">              2470</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Crewplanet SIA</t>
+          <t>Manta Systems AB</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-93718.46000000001</v>
+        <v>-95.84999999999999</v>
       </c>
       <c r="D119" t="n">
-        <v>-93718</v>
+        <v>-96</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>LV40003789592</t>
+          <t>SE559457660401</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">               907</t>
+          <t xml:space="preserve">              1437</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>HANSAEL SIA</t>
+          <t>Q Workforce</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="D120" t="n">
-        <v>-25</v>
+        <v>-5</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>LV40003660806</t>
+          <t>SE559200270201</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2805</t>
+          <t xml:space="preserve">              1075</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Martide Manning Latvia SIA</t>
+          <t>Rederi AB Donsötank - EUR</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-198</v>
+        <v>-397</v>
       </c>
       <c r="D121" t="n">
-        <v>-198</v>
+        <v>-397</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>LV40203626599</t>
+          <t>SE556058292501</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">               340</t>
+          <t xml:space="preserve">              1655</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>RIX Shipmanagement LTD</t>
+          <t>Sirius Shipping</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-15969.25</v>
+        <v>-448</v>
       </c>
       <c r="D122" t="n">
-        <v>-15969</v>
+        <v>-448</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>LV40103681236</t>
+          <t>SE556772536001</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">               751</t>
+          <t xml:space="preserve">               962</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>SIA OJ CREW RIGA</t>
+          <t>VERITAS MANAGEMENT AB</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>25</v>
+        <v>-67</v>
       </c>
       <c r="D123" t="n">
-        <v>25</v>
+        <v>-67</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>LV50203144731</t>
+          <t>SE559003939101</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Sweden</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2420</t>
+          <t xml:space="preserve">              2580</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>SIA OJ Travel</t>
+          <t>West Atlantic Sweden AB</t>
         </is>
       </c>
       <c r="C124" t="n">
-        <v>-15578.39</v>
+        <v>-104</v>
       </c>
       <c r="D124" t="n">
-        <v>-15578</v>
+        <v>-104</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>LV40003286572</t>
+          <t>SE556062442001</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1091</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>UNION AVIATION AS</t>
-        </is>
-      </c>
-      <c r="C125" t="n">
-        <v>-8950.35</v>
-      </c>
-      <c r="D125" t="n">
-        <v>-8950</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>LV40203294676</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>Latvia</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2742</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>BALTNAUTIC SHIPPING LTD</t>
-        </is>
-      </c>
-      <c r="C126" t="n">
-        <v>-1422.44</v>
-      </c>
-      <c r="D126" t="n">
-        <v>-1422</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>LT417071917</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Lithuania</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               569</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>GEO@SEA Luxembourg S.A.</t>
-        </is>
-      </c>
-      <c r="C127" t="n">
-        <v>-6290.82</v>
-      </c>
-      <c r="D127" t="n">
-        <v>-6291</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>LU32235384</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>Luxembourg</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2964</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>MV KAREWOOD BRAVE — IMO 9281516</t>
-        </is>
-      </c>
-      <c r="C128" t="n">
-        <v>-60</v>
-      </c>
-      <c r="D128" t="n">
-        <v>-60</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>MT24502936</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>MALTA</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               862</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Atlantis Tankers Group (Malta) Ltd.</t>
-        </is>
-      </c>
-      <c r="C129" t="n">
-        <v>-344.24</v>
-      </c>
-      <c r="D129" t="n">
-        <v>-344</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>MT21829715</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1465</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>CldN Malta Ltd.</t>
-        </is>
-      </c>
-      <c r="C130" t="n">
-        <v>-28320.51</v>
-      </c>
-      <c r="D130" t="n">
-        <v>-28321</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>MT22140026</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1415</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>DC Aviation Ltd.</t>
-        </is>
-      </c>
-      <c r="C131" t="n">
-        <v>-1023.68</v>
-      </c>
-      <c r="D131" t="n">
-        <v>-1024</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>MT18886308</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2194</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Elit’Avia Malta Ltd</t>
-        </is>
-      </c>
-      <c r="C132" t="n">
-        <v>-5560.25</v>
-      </c>
-      <c r="D132" t="n">
-        <v>-5560</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>MT19960414</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               218</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>FT Portoria Tankers Ltd</t>
-        </is>
-      </c>
-      <c r="C133" t="n">
-        <v>-351.6</v>
-      </c>
-      <c r="D133" t="n">
-        <v>-352</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>MT22398518</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               718</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Furtrans Tanker Holdings Ltd</t>
-        </is>
-      </c>
-      <c r="C134" t="n">
-        <v>-2381.7</v>
-      </c>
-      <c r="D134" t="n">
-        <v>-2382</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>MT26731101</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2408</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Hans Travel Ltd</t>
-        </is>
-      </c>
-      <c r="C135" t="n">
-        <v>250</v>
-      </c>
-      <c r="D135" t="n">
-        <v>250</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>MT28450014</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2939</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>Lighthouse Yachting Malta Limited</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>-246.52</v>
-      </c>
-      <c r="D136" t="n">
-        <v>-247</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>MT29674336</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2963</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>MV KAREWOOD GLORY — IMO 9281504</t>
-        </is>
-      </c>
-      <c r="C137" t="n">
-        <v>-177.78</v>
-      </c>
-      <c r="D137" t="n">
-        <v>-178</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>MT24503928</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2995</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>MV KAREWOOD PRIDE — IMO 9281499</t>
-        </is>
-      </c>
-      <c r="C138" t="n">
-        <v>-90</v>
-      </c>
-      <c r="D138" t="n">
-        <v>-90</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>MT24503035</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2992</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>MV KAREWOOD STAR — IMO 9363986</t>
-        </is>
-      </c>
-      <c r="C139" t="n">
-        <v>-107.81</v>
-      </c>
-      <c r="D139" t="n">
-        <v>-108</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>MT24503217</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2037</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>-1030.85</v>
-      </c>
-      <c r="D140" t="n">
-        <v>-1031</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>MT27270636</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2036</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Quinto Tankers Ltd</t>
-        </is>
-      </c>
-      <c r="C141" t="n">
-        <v>-535.17</v>
-      </c>
-      <c r="D141" t="n">
-        <v>-535</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>MT27591013</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               826</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>SL Ship Management Ltd</t>
-        </is>
-      </c>
-      <c r="C142" t="n">
-        <v>-1589.04</v>
-      </c>
-      <c r="D142" t="n">
-        <v>-1589</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>MT18726720</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2105</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>ZuluWaves Limited</t>
-        </is>
-      </c>
-      <c r="C143" t="n">
-        <v>-2410.24</v>
-      </c>
-      <c r="D143" t="n">
-        <v>-2410</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>MT30851503</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>Malta</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              3110</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Arion Retail Group Poland Sp. z o.o.</t>
-        </is>
-      </c>
-      <c r="C144" t="n">
-        <v>-18</v>
-      </c>
-      <c r="D144" t="n">
-        <v>-18</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>PL5253064487</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>Poland</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               679</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Afonso Ferreira Faria unipessoal LDa</t>
-        </is>
-      </c>
-      <c r="C145" t="n">
-        <v>-4531.1</v>
-      </c>
-      <c r="D145" t="n">
-        <v>-4531</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>PT513880151</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              3008</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>JetUp, Lda.</t>
-        </is>
-      </c>
-      <c r="C146" t="n">
-        <v>-1383</v>
-      </c>
-      <c r="D146" t="n">
-        <v>-1383</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>PT518498298</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1031</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
-        </is>
-      </c>
-      <c r="C147" t="n">
-        <v>-1302.34</v>
-      </c>
-      <c r="D147" t="n">
-        <v>-1302</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>PT502635770</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2133</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Tulipa Mensageira LDA</t>
-        </is>
-      </c>
-      <c r="C148" t="n">
-        <v>-3732.06</v>
-      </c>
-      <c r="D148" t="n">
-        <v>-3732</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>PT517035863</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>Portugal</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              3109</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Arion Retail Group Romania S.R.L.</t>
-        </is>
-      </c>
-      <c r="C149" t="n">
-        <v>2.664535259100376e-15</v>
-      </c>
-      <c r="D149" t="n">
-        <v>0</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>RO52745394</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>Romania</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2097</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>JET ADVISOR</t>
-        </is>
-      </c>
-      <c r="C150" t="n">
-        <v>-268.3</v>
-      </c>
-      <c r="D150" t="n">
-        <v>-268</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>RO28308419</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>Romania</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1577</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>S.C. TOYO AVIATION S.R.L.</t>
-        </is>
-      </c>
-      <c r="C151" t="n">
-        <v>-2950.35</v>
-      </c>
-      <c r="D151" t="n">
-        <v>-2950</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>RO21977513</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>Romania</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               420</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Zumaia Offshore, S.L.</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>-1529.27</v>
-      </c>
-      <c r="D152" t="n">
-        <v>-1529</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>ESB95442182</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>SPAIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               909</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>ERZOFF-SHORE, S.L.</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>-83.71000000000001</v>
-      </c>
-      <c r="D153" t="n">
-        <v>-84</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>ESB06919351</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2236</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Espana Rope Access Solutions SL</t>
-        </is>
-      </c>
-      <c r="C154" t="n">
-        <v>-2593.03</v>
-      </c>
-      <c r="D154" t="n">
-        <v>-2593</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>ESB09880675</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2389</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Geoxyz Spain SL</t>
-        </is>
-      </c>
-      <c r="C155" t="n">
-        <v>-218.34</v>
-      </c>
-      <c r="D155" t="n">
-        <v>-218</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>ESB13905591</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>Spain</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2471</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>C Survey</t>
-        </is>
-      </c>
-      <c r="C156" t="n">
-        <v>-529.09</v>
-      </c>
-      <c r="D156" t="n">
-        <v>-529</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>SE556782721601</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2670</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Fjordtank Rederi AB</t>
-        </is>
-      </c>
-      <c r="C157" t="n">
-        <v>-551.21</v>
-      </c>
-      <c r="D157" t="n">
-        <v>-551</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>SE556633100401</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              3135</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>FureBear AB</t>
-        </is>
-      </c>
-      <c r="C158" t="n">
-        <v>-30</v>
-      </c>
-      <c r="D158" t="n">
-        <v>-30</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>SE559389323201</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              3133</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Furetank Rederi AB</t>
-        </is>
-      </c>
-      <c r="C159" t="n">
-        <v>-316.69</v>
-      </c>
-      <c r="D159" t="n">
-        <v>-317</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>SE556371751001</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2692</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>HF Interior AB</t>
-        </is>
-      </c>
-      <c r="C160" t="n">
-        <v>-559.29</v>
-      </c>
-      <c r="D160" t="n">
-        <v>-559</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>SE556844774101</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               725</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Linnea Shipping A/S</t>
-        </is>
-      </c>
-      <c r="C161" t="n">
-        <v>-2777.19</v>
-      </c>
-      <c r="D161" t="n">
-        <v>-2777</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>SE556405820301</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2470</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>Manta Systems AB</t>
-        </is>
-      </c>
-      <c r="C162" t="n">
-        <v>-348.08</v>
-      </c>
-      <c r="D162" t="n">
-        <v>-348</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>SE559457660401</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               616</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>OljOla Shipping AB</t>
-        </is>
-      </c>
-      <c r="C163" t="n">
-        <v>-339.67</v>
-      </c>
-      <c r="D163" t="n">
-        <v>-340</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>SE559151957301</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1437</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Q Workforce</t>
-        </is>
-      </c>
-      <c r="C164" t="n">
-        <v>-921.9</v>
-      </c>
-      <c r="D164" t="n">
-        <v>-922</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>SE559200270201</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1075</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>Rederi AB Donsötank - EUR</t>
-        </is>
-      </c>
-      <c r="C165" t="n">
-        <v>-4743.49</v>
-      </c>
-      <c r="D165" t="n">
-        <v>-4743</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>SE556058292501</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2735</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Sirius Agency</t>
-        </is>
-      </c>
-      <c r="C166" t="n">
-        <v>50</v>
-      </c>
-      <c r="D166" t="n">
-        <v>50</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>SE556043575101</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              1655</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>Sirius Shipping</t>
-        </is>
-      </c>
-      <c r="C167" t="n">
-        <v>-7556.64</v>
-      </c>
-      <c r="D167" t="n">
-        <v>-7557</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>SE556772536001</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t xml:space="preserve">               962</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>VERITAS MANAGEMENT AB</t>
-        </is>
-      </c>
-      <c r="C168" t="n">
-        <v>-2697.02</v>
-      </c>
-      <c r="D168" t="n">
-        <v>-2697</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>SE559003939101</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>Sweden</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t xml:space="preserve">              2580</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>West Atlantic Sweden AB</t>
-        </is>
-      </c>
-      <c r="C169" t="n">
-        <v>-2523.14</v>
-      </c>
-      <c r="D169" t="n">
-        <v>-2523</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>SE556062442001</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>

--- a/output/ICP Q2'26.xlsx
+++ b/output/ICP Q2'26.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F124"/>
+  <dimension ref="A1:F169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,23 +451,23 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2534</t>
+          <t xml:space="preserve">              2358</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>JetView GmbH</t>
+          <t>AXIS Aviation Austria GmbH</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-459.99</v>
+        <v>-49.8</v>
       </c>
       <c r="D2" t="n">
-        <v>-460</v>
+        <v>-50</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ATU78020035</t>
+          <t>ATU78323306</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -479,51 +479,51 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3114</t>
+          <t xml:space="preserve">              2534</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Arion Retail Group Belgium</t>
+          <t>JetView GmbH</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-30</v>
+        <v>-785.48</v>
       </c>
       <c r="D3" t="n">
-        <v>-30</v>
+        <v>-785</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>BE1014587039</t>
+          <t>ATU78020035</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Belgium</t>
+          <t>Austria</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t xml:space="preserve">               883</t>
+          <t xml:space="preserve">              3114</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Fugro Belgium BV</t>
+          <t>Arion Retail Group Belgium</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-1541</v>
+        <v>-30</v>
       </c>
       <c r="D4" t="n">
-        <v>-1541</v>
+        <v>-30</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>BE0403026288</t>
+          <t>BE1014587039</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -535,23 +535,23 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t xml:space="preserve">               493</t>
+          <t xml:space="preserve">               883</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>GEOxyz bvba</t>
+          <t>Fugro Belgium BV</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-149.24</v>
+        <v>-1541</v>
       </c>
       <c r="D5" t="n">
-        <v>-149</v>
+        <v>-1541</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>BE0465233774</t>
+          <t>BE0403026288</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -563,23 +563,23 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t xml:space="preserve">               596</t>
+          <t xml:space="preserve">               493</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Geo Aqua bvba</t>
+          <t>GEOxyz bvba</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-94.25</v>
+        <v>-5188.39</v>
       </c>
       <c r="D6" t="n">
-        <v>-94</v>
+        <v>-5188</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>BE0890302622</t>
+          <t>BE0465233774</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -591,23 +591,23 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t xml:space="preserve">               237</t>
+          <t xml:space="preserve">               596</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>International Food Services NV</t>
+          <t>Geo Aqua bvba</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-409.74</v>
+        <v>-1604.84</v>
       </c>
       <c r="D7" t="n">
-        <v>-410</v>
+        <v>-1605</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>BE0472409202</t>
+          <t>BE0890302622</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -619,23 +619,23 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2968</t>
+          <t xml:space="preserve">               237</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Subsea Global Solutions Belgium BV</t>
+          <t>International Food Services NV</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-750</v>
+        <v>-1689.57</v>
       </c>
       <c r="D8" t="n">
-        <v>-750</v>
+        <v>-1690</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>BE0502793758</t>
+          <t>BE0472409202</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -647,79 +647,79 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2920</t>
+          <t xml:space="preserve">              3070</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Dark Waves Ltd</t>
+          <t>Seasoils (Enviros)</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-534</v>
+        <v>-187.8</v>
       </c>
       <c r="D9" t="n">
-        <v>-534</v>
+        <v>-188</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>BG207801369</t>
+          <t>BE0515949235</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belgium</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2652</t>
+          <t xml:space="preserve">              2968</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Hit Tourism LTD</t>
+          <t>Subsea Global Solutions Belgium BV</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-772.45</v>
+        <v>-750</v>
       </c>
       <c r="D10" t="n">
-        <v>-772</v>
+        <v>-750</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>BG103594726</t>
+          <t>BE0502793758</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bulgaria</t>
+          <t>Belgium</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2918</t>
+          <t xml:space="preserve">              2920</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>windshipping</t>
+          <t>Dark Waves Ltd</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-21</v>
+        <v>-1964.04</v>
       </c>
       <c r="D11" t="n">
-        <v>-21</v>
+        <v>-1964</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>BG205047575</t>
+          <t>BG207801369</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -731,135 +731,135 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2404</t>
+          <t xml:space="preserve">              2652</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Marine Air Split</t>
+          <t>Hit Tourism LTD</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-795</v>
+        <v>-13274.05</v>
       </c>
       <c r="D12" t="n">
-        <v>-795</v>
+        <v>-13274</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>HR90789004458</t>
+          <t>BG103594726</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Croatia</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t xml:space="preserve">               136</t>
+          <t xml:space="preserve">               404</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Asia Marine Philippines</t>
+          <t>Visitship Ltd</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-9</v>
+        <v>-50</v>
       </c>
       <c r="D13" t="n">
-        <v>-9</v>
+        <v>-50</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>CY10342881S</t>
+          <t>BG204690910</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1439</t>
+          <t xml:space="preserve">              2918</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Atlas Inexco CY Ltd.</t>
+          <t>windshipping</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-237</v>
+        <v>-4035.02</v>
       </c>
       <c r="D14" t="n">
-        <v>-237</v>
+        <v>-4035</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>CY10342092N</t>
+          <t>BG205047575</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Bulgaria</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2807</t>
+          <t xml:space="preserve">              2404</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Caribbean Shipping Ltd</t>
+          <t>Marine Air Split</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-148</v>
+        <v>-1255.77</v>
       </c>
       <c r="D15" t="n">
-        <v>-148</v>
+        <v>-1256</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>CY10303314V</t>
+          <t>HR90789004458</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Cyprus</t>
+          <t>Croatia</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t xml:space="preserve">               658</t>
+          <t xml:space="preserve">               136</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Henley Travel LTD</t>
+          <t>Asia Marine Philippines</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-167.56</v>
+        <v>-12520.16</v>
       </c>
       <c r="D16" t="n">
-        <v>-168</v>
+        <v>-12520</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>CY10110942W</t>
+          <t>CY10342881S</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -871,23 +871,23 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1191</t>
+          <t xml:space="preserve">              1439</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>IO Line Limited</t>
+          <t>Atlas Inexco CY Ltd.</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-10</v>
+        <v>-390.36</v>
       </c>
       <c r="D17" t="n">
-        <v>-10</v>
+        <v>-390</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>CY10440516Z</t>
+          <t>CY10342092N</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -899,23 +899,23 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3117</t>
+          <t xml:space="preserve">               488</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>OSM SHIP MANAGEMENT CYPRUS LTD</t>
+          <t>Cymare Shipmanagement Ltd</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-17.15</v>
+        <v>-200</v>
       </c>
       <c r="D18" t="n">
-        <v>-17</v>
+        <v>-200</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CY10377387I</t>
+          <t>CY10309832T</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -927,23 +927,23 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1210</t>
+          <t xml:space="preserve">              2809</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Ocean Advice Ltd.</t>
+          <t>Eurica Shipping Ltd</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-243</v>
+        <v>-2495.29</v>
       </c>
       <c r="D19" t="n">
-        <v>-243</v>
+        <v>-2495</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>CY10438212J</t>
+          <t>CY10303314V</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -955,23 +955,23 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t xml:space="preserve">               375</t>
+          <t xml:space="preserve">               658</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>SMT SHIPPING (CYPRUS ) LTD</t>
+          <t>Henley Travel LTD</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-1101.06</v>
+        <v>-6802.47</v>
       </c>
       <c r="D20" t="n">
-        <v>-1101</v>
+        <v>-6802</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>CY10039349U</t>
+          <t>CY10110942W</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -983,23 +983,23 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t xml:space="preserve">               204</t>
+          <t xml:space="preserve">              1191</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Scylla Gastro Ltd</t>
+          <t>IO Line Limited</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-2760.21</v>
+        <v>-56.8</v>
       </c>
       <c r="D21" t="n">
-        <v>-2760</v>
+        <v>-57</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>CY10318112E</t>
+          <t>CY10440516Z</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1011,23 +1011,23 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t xml:space="preserve">               498</t>
+          <t xml:space="preserve">              1520</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Scylla Nautic Ltd</t>
+          <t>Lowland International Shipping Cyprus Ltd</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-2002.81</v>
+        <v>-1566.14</v>
       </c>
       <c r="D22" t="n">
-        <v>-2003</v>
+        <v>-1566</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>CY10338093B</t>
+          <t>CY10252740F</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1039,275 +1039,275 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1579</t>
+          <t xml:space="preserve">              2446</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cyan Renewables Aps</t>
+          <t>OPEN OCEAN SERVICES LTD</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-250</v>
+        <v>-179.99</v>
       </c>
       <c r="D23" t="n">
-        <v>-250</v>
+        <v>-180</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>DK43887904</t>
+          <t>CY60023930P</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1628</t>
+          <t xml:space="preserve">              3117</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Cyan Renewables ac1  Aps</t>
+          <t>OSM SHIP MANAGEMENT CYPRUS LTD</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>-494.76</v>
+        <v>-1749.23</v>
       </c>
       <c r="D24" t="n">
-        <v>-495</v>
+        <v>-1749</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>DK43958496</t>
+          <t>CY10377387I</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2901</t>
+          <t xml:space="preserve">              1210</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>ESVAGT A/S</t>
+          <t>Ocean Advice Ltd.</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>-974</v>
+        <v>-1284.01</v>
       </c>
       <c r="D25" t="n">
-        <v>-974</v>
+        <v>-1284</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>DK60698813</t>
+          <t>CY10438212J</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t xml:space="preserve">               667</t>
+          <t xml:space="preserve">               337</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MHO Operations ApS</t>
+          <t>Reederei Nord Shipmanagement Ltd.</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>-442.3</v>
+        <v>-1171.65</v>
       </c>
       <c r="D26" t="n">
-        <v>-442</v>
+        <v>-1172</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>DK38948563</t>
+          <t>CY10344686Z</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2347</t>
+          <t xml:space="preserve">               369</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>SHIP 103 ApS</t>
+          <t>SEACREW MANAGEMENT LTD</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>-89.53999999999999</v>
+        <v>-1958.39</v>
       </c>
       <c r="D27" t="n">
-        <v>-90</v>
+        <v>-1958</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>DK40344446</t>
+          <t>CY10205318D</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1295</t>
+          <t xml:space="preserve">               375</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Ship 102 ApS</t>
+          <t>SMT SHIPPING (CYPRUS ) LTD</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>-40</v>
+        <v>-2567.3</v>
       </c>
       <c r="D28" t="n">
-        <v>-40</v>
+        <v>-2567</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>DK43303384</t>
+          <t>CY10039349U</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2348</t>
+          <t xml:space="preserve">               204</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Ship 104 ApS</t>
+          <t>Scylla Gastro Ltd</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>-107.92</v>
+        <v>-35927.77</v>
       </c>
       <c r="D29" t="n">
-        <v>-108</v>
+        <v>-35928</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>DK44210096</t>
+          <t>CY10318112E</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2349</t>
+          <t xml:space="preserve">               498</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Ship 105 ApS</t>
+          <t>Scylla Nautic Ltd</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>-26.38</v>
+        <v>-28485.84</v>
       </c>
       <c r="D30" t="n">
-        <v>-26</v>
+        <v>-28486</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>DK44210126</t>
+          <t>CY10338093B</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t xml:space="preserve">               123</t>
+          <t xml:space="preserve">              2650</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>TORM A/S</t>
+          <t>Unipolar Shipping Limited</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>-29.83</v>
+        <v>-588.8</v>
       </c>
       <c r="D31" t="n">
-        <v>-30</v>
+        <v>-589</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>DK22460218</t>
+          <t>CY60083461Z</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Denmark</t>
+          <t>Cyprus</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1424</t>
+          <t xml:space="preserve">               868</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Terntank Rederi A/S</t>
+          <t>C-bed Holding A/S</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>-135.05</v>
+        <v>-85.5</v>
       </c>
       <c r="D32" t="n">
-        <v>-135</v>
+        <v>-86</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>DK34584362</t>
+          <t>DK37183555</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1319,863 +1319,863 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t xml:space="preserve">               128</t>
+          <t xml:space="preserve">              3056</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Amisco AS</t>
+          <t>Christiania Shipping A/S</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>-1432</v>
+        <v>-167</v>
       </c>
       <c r="D33" t="n">
-        <v>-1432</v>
+        <v>-167</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>EE100100240</t>
+          <t>DK40533516</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1524</t>
+          <t xml:space="preserve">              1579</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Atrica-Marine OU</t>
+          <t>Cyan Renewables Aps</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>-22</v>
+        <v>-712.84</v>
       </c>
       <c r="D34" t="n">
-        <v>-22</v>
+        <v>-713</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>EE100218912</t>
+          <t>DK43887904</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2267</t>
+          <t xml:space="preserve">              1628</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>FinMetalock</t>
+          <t>Cyan Renewables ac1  Aps</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>-146</v>
+        <v>-3597.96</v>
       </c>
       <c r="D35" t="n">
-        <v>-146</v>
+        <v>-3598</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>EE101329758</t>
+          <t>DK43958496</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t xml:space="preserve">               548</t>
+          <t xml:space="preserve">              2901</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Klip Marine Shipmanagement Ltd</t>
+          <t>ESVAGT A/S</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>-46</v>
+        <v>-3569.81</v>
       </c>
       <c r="D36" t="n">
-        <v>-46</v>
+        <v>-3570</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>EE101033617</t>
+          <t>DK60698813</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t xml:space="preserve">               986</t>
+          <t xml:space="preserve">               667</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>OU VLM REPAIR</t>
+          <t>MHO Operations ApS</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>-656</v>
+        <v>-4357.16</v>
       </c>
       <c r="D37" t="n">
-        <v>-656</v>
+        <v>-4357</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>EE101606918</t>
+          <t>DK38948563</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2095</t>
+          <t xml:space="preserve">               840</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Swaileap OÜ LSA</t>
+          <t>Ocean Zephyr ApS</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>-15</v>
+        <v>-1270.86</v>
       </c>
       <c r="D38" t="n">
-        <v>-15</v>
+        <v>-1271</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>EE102074617</t>
+          <t>DK41294574</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2310</t>
+          <t xml:space="preserve">              2347</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>TS Shipping OÜ</t>
+          <t>SHIP 103 ApS</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>-271</v>
+        <v>-702.9400000000001</v>
       </c>
       <c r="D39" t="n">
-        <v>-271</v>
+        <v>-703</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>EE101597632</t>
+          <t>DK40344446</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t xml:space="preserve">               391</t>
+          <t xml:space="preserve">              1080</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Tschudi Ship Management AS</t>
+          <t>Ship 101 ApS</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>-17</v>
+        <v>-164.82</v>
       </c>
       <c r="D40" t="n">
-        <v>-17</v>
+        <v>-165</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>EE100708642</t>
+          <t>DK43303414</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Estonia</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t xml:space="preserve">               206</t>
+          <t xml:space="preserve">              1295</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ESL Shipping Oy</t>
+          <t>Ship 102 ApS</t>
         </is>
       </c>
       <c r="C41" t="n">
-        <v>-1295</v>
+        <v>-804.0600000000001</v>
       </c>
       <c r="D41" t="n">
-        <v>-1295</v>
+        <v>-804</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>FI02011264</t>
+          <t>DK43303384</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3124</t>
+          <t xml:space="preserve">              2348</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Oy AtoB@C Shipping Ab</t>
+          <t>Ship 104 ApS</t>
         </is>
       </c>
       <c r="C42" t="n">
-        <v>0</v>
+        <v>-848.9200000000001</v>
       </c>
       <c r="D42" t="n">
-        <v>0</v>
+        <v>-849</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>FI25781405</t>
+          <t>DK44210096</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t xml:space="preserve">               334</t>
+          <t xml:space="preserve">              2349</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Rederi ab Nathalie</t>
+          <t>Ship 105 ApS</t>
         </is>
       </c>
       <c r="C43" t="n">
-        <v>-117</v>
+        <v>-184.18</v>
       </c>
       <c r="D43" t="n">
-        <v>-117</v>
+        <v>-184</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>FI22811672</t>
+          <t>DK44210126</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Finland</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t xml:space="preserve">               965</t>
+          <t xml:space="preserve">               380</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>COMPAGNIE DU PONANT</t>
+          <t>Svendborg Bugser A/S</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>-2284</v>
+        <v>-307.25</v>
       </c>
       <c r="D44" t="n">
-        <v>-2284</v>
+        <v>-307</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>FR83344497011</t>
+          <t>DK21792802</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t xml:space="preserve">               564</t>
+          <t xml:space="preserve">               123</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GeoXYZ sarl</t>
+          <t>TORM A/S</t>
         </is>
       </c>
       <c r="C45" t="n">
-        <v>-20</v>
+        <v>-285.75</v>
       </c>
       <c r="D45" t="n">
-        <v>-20</v>
+        <v>-286</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>FR90507902211</t>
+          <t>DK22460218</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2490</t>
+          <t xml:space="preserve">              1424</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PXGEO France SAS</t>
+          <t>Terntank Rederi A/S</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>-700.28</v>
+        <v>-6974.43</v>
       </c>
       <c r="D46" t="n">
-        <v>-700</v>
+        <v>-6974</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>FR70918328766</t>
+          <t>DK34584362</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>Denmark</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t xml:space="preserve">               382</t>
+          <t xml:space="preserve">               128</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>THENAMARIS SHIPS MANAGEMENT INC</t>
+          <t>Amisco AS</t>
         </is>
       </c>
       <c r="C47" t="n">
-        <v>-656.14</v>
+        <v>-4721.84</v>
       </c>
       <c r="D47" t="n">
-        <v>-656</v>
+        <v>-4722</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>EL098010844</t>
+          <t>EE100100240</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>GREECE</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2450</t>
+          <t xml:space="preserve">              1524</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Air Partner International GmbH</t>
+          <t>Atrica-Marine OU</t>
         </is>
       </c>
       <c r="C48" t="n">
-        <v>-92.99000000000001</v>
+        <v>-1250.64</v>
       </c>
       <c r="D48" t="n">
-        <v>-93</v>
+        <v>-1251</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>DE184629207</t>
+          <t>EE100218912</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t xml:space="preserve">               152</t>
+          <t xml:space="preserve">              2267</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Axxaz Europe GmbH</t>
+          <t>FinMetalock</t>
         </is>
       </c>
       <c r="C49" t="n">
-        <v>-773</v>
+        <v>-1709.78</v>
       </c>
       <c r="D49" t="n">
-        <v>-773</v>
+        <v>-1710</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>DE296988120</t>
+          <t>EE101329758</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2736</t>
+          <t xml:space="preserve">              2798</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Beteiligungsgesellschaft MS Santa Vanessa mbH &amp; Co</t>
+          <t>HFH Grupp OÜ</t>
         </is>
       </c>
       <c r="C50" t="n">
-        <v>-23</v>
+        <v>-325</v>
       </c>
       <c r="D50" t="n">
-        <v>-23</v>
+        <v>-325</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>DE232610165</t>
+          <t>EE101584289</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2319</t>
+          <t xml:space="preserve">               548</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
+          <t>Klip Marine Shipmanagement Ltd</t>
         </is>
       </c>
       <c r="C51" t="n">
-        <v>-85</v>
+        <v>-653.11</v>
       </c>
       <c r="D51" t="n">
-        <v>-85</v>
+        <v>-653</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>DE249771948</t>
+          <t>EE101033617</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2318</t>
+          <t xml:space="preserve">               986</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
+          <t>OU VLM REPAIR</t>
         </is>
       </c>
       <c r="C52" t="n">
-        <v>-42</v>
+        <v>-3310.88</v>
       </c>
       <c r="D52" t="n">
-        <v>-42</v>
+        <v>-3311</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>DE213881581</t>
+          <t>EE101606918</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2107</t>
+          <t xml:space="preserve">              2095</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
+          <t>Swaileap OÜ LSA</t>
         </is>
       </c>
       <c r="C53" t="n">
-        <v>-745</v>
+        <v>-6278.9</v>
       </c>
       <c r="D53" t="n">
-        <v>-745</v>
+        <v>-6279</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>DE293561563</t>
+          <t>EE102074617</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1169</t>
+          <t xml:space="preserve">              2310</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>EMS Crewing GmbH</t>
+          <t>TS Shipping OÜ</t>
         </is>
       </c>
       <c r="C54" t="n">
-        <v>-26</v>
+        <v>-617.74</v>
       </c>
       <c r="D54" t="n">
-        <v>-26</v>
+        <v>-618</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>DE262060886</t>
+          <t>EE101597632</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2284</t>
+          <t xml:space="preserve">               391</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Hansa Safety Services GmbH</t>
+          <t>Tschudi Ship Management AS</t>
         </is>
       </c>
       <c r="C55" t="n">
-        <v>-663.23</v>
+        <v>-1149.14</v>
       </c>
       <c r="D55" t="n">
-        <v>-663</v>
+        <v>-1149</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>DE284814823</t>
+          <t>EE100708642</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Estonia</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2016</t>
+          <t xml:space="preserve">               206</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>KG MS CPO BARCELONA Offen Reederei UG (haftungsbes</t>
+          <t>ESL Shipping Oy</t>
         </is>
       </c>
       <c r="C56" t="n">
-        <v>-108</v>
+        <v>-7939.44</v>
       </c>
       <c r="D56" t="n">
-        <v>-108</v>
+        <v>-7939</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>DE298771680</t>
+          <t>FI02011264</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2376</t>
+          <t xml:space="preserve">              3124</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
+          <t>Oy AtoB@C Shipping Ab</t>
         </is>
       </c>
       <c r="C57" t="n">
-        <v>-21</v>
+        <v>2.664535259100376e-15</v>
       </c>
       <c r="D57" t="n">
-        <v>-21</v>
+        <v>0</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>DE257260686</t>
+          <t>FI25781405</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2684</t>
+          <t xml:space="preserve">               334</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Martide Holding GmbH</t>
+          <t>Rederi ab Nathalie</t>
         </is>
       </c>
       <c r="C58" t="n">
-        <v>-50</v>
+        <v>-2854.89</v>
       </c>
       <c r="D58" t="n">
-        <v>-50</v>
+        <v>-2855</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>DE450210277</t>
+          <t>FI22811672</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Finland</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t xml:space="preserve">               309</t>
+          <t xml:space="preserve">               965</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>NSB Crewing Solutions</t>
+          <t>COMPAGNIE DU PONANT</t>
         </is>
       </c>
       <c r="C59" t="n">
-        <v>-15</v>
+        <v>-2274.5</v>
       </c>
       <c r="D59" t="n">
-        <v>-15</v>
+        <v>-2274</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>DE283269969</t>
+          <t>FR83344497011</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t xml:space="preserve">               310</t>
+          <t xml:space="preserve">               564</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>NSB Reederei GmbH &amp; Co. Kg</t>
+          <t>GeoXYZ sarl</t>
         </is>
       </c>
       <c r="C60" t="n">
-        <v>-93.2</v>
+        <v>-446.08</v>
       </c>
       <c r="D60" t="n">
-        <v>-93</v>
+        <v>-446</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>DE116474094</t>
+          <t>FR90507902211</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2238</t>
+          <t xml:space="preserve">              2490</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
+          <t>PXGEO France SAS</t>
         </is>
       </c>
       <c r="C61" t="n">
-        <v>-21</v>
+        <v>-1437.91</v>
       </c>
       <c r="D61" t="n">
-        <v>-21</v>
+        <v>-1438</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>DE362363142</t>
+          <t>FR70918328766</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>France</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t xml:space="preserve">               298</t>
+          <t xml:space="preserve">               382</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Nordic Hamburg Crewing Services GmbH</t>
+          <t>THENAMARIS SHIPS MANAGEMENT INC</t>
         </is>
       </c>
       <c r="C62" t="n">
-        <v>-1878</v>
+        <v>-22</v>
       </c>
       <c r="D62" t="n">
-        <v>-1878</v>
+        <v>-22</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>DE309948810</t>
+          <t>EL098010844</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>GREECE</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2678</t>
+          <t xml:space="preserve">               945</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
+          <t>AMARO Travel GmbH</t>
         </is>
       </c>
       <c r="C63" t="n">
-        <v>-1631.97</v>
+        <v>-53.6</v>
       </c>
       <c r="D63" t="n">
-        <v>-1632</v>
+        <v>-54</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>DE285660591</t>
+          <t>DE309139121</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2187,23 +2187,23 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3064</t>
+          <t xml:space="preserve">              2450</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OBC by Avico GmbH</t>
+          <t>Air Partner International GmbH</t>
         </is>
       </c>
       <c r="C64" t="n">
-        <v>-72.99000000000001</v>
+        <v>-672.04</v>
       </c>
       <c r="D64" t="n">
-        <v>-73</v>
+        <v>-672</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>DE457137561</t>
+          <t>DE184629207</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2215,23 +2215,23 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1498</t>
+          <t xml:space="preserve">              1576</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Reederei F. Laeisz GmbH</t>
+          <t>Andreas Zerr</t>
         </is>
       </c>
       <c r="C65" t="n">
-        <v>-84</v>
+        <v>-173.2</v>
       </c>
       <c r="D65" t="n">
-        <v>-84</v>
+        <v>-173</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>DE811585869</t>
+          <t>DE221230922</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2243,23 +2243,23 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3017</t>
+          <t xml:space="preserve">               152</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>SUNDAIR Gmbh</t>
+          <t>Axxaz Europe GmbH</t>
         </is>
       </c>
       <c r="C66" t="n">
-        <v>-192</v>
+        <v>-19230.99</v>
       </c>
       <c r="D66" t="n">
-        <v>-192</v>
+        <v>-19231</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>DE305307186</t>
+          <t>DE296988120</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2271,23 +2271,23 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3026</t>
+          <t xml:space="preserve">              2736</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>T &amp; T In Situ Machining GmbH</t>
+          <t>Beteiligungsgesellschaft MS Santa Vanessa mbH &amp; Co</t>
         </is>
       </c>
       <c r="C67" t="n">
-        <v>-543.9400000000001</v>
+        <v>-23</v>
       </c>
       <c r="D67" t="n">
-        <v>-544</v>
+        <v>-23</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>DE327579122</t>
+          <t>DE232610165</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2299,23 +2299,23 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t xml:space="preserve">               832</t>
+          <t xml:space="preserve">              2319</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>UHL Chartering GmbH &amp; Co. KG</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Ace - 2520</t>
         </is>
       </c>
       <c r="C68" t="n">
-        <v>-436.86</v>
+        <v>-85</v>
       </c>
       <c r="D68" t="n">
-        <v>-437</v>
+        <v>-85</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>DE350330837</t>
+          <t>DE249771948</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2327,23 +2327,23 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1065</t>
+          <t xml:space="preserve">              2318</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>UHL Crewing GmbH</t>
+          <t>CPO Crewing GmbH &amp; Co. KG for MV RDO Bremen - 2523</t>
         </is>
       </c>
       <c r="C69" t="n">
-        <v>-983</v>
+        <v>-42</v>
       </c>
       <c r="D69" t="n">
-        <v>-983</v>
+        <v>-42</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>DE330510394</t>
+          <t>DE213881581</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2355,23 +2355,23 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t xml:space="preserve">               396</t>
+          <t xml:space="preserve">              2594</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>USC Crew GmbH</t>
+          <t>CPO Crewing GmbH &amp; Co. KG forRDO Endeavour - 2522</t>
         </is>
       </c>
       <c r="C70" t="n">
-        <v>-140.72</v>
+        <v>-196.47</v>
       </c>
       <c r="D70" t="n">
-        <v>-141</v>
+        <v>-196</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>DE274971782</t>
+          <t>DE307865976</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2383,23 +2383,23 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3065</t>
+          <t xml:space="preserve">              2107</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>USC GmbH</t>
+          <t>CSN Crane Service North GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C71" t="n">
-        <v>-256.19</v>
+        <v>-2683.32</v>
       </c>
       <c r="D71" t="n">
-        <v>-256</v>
+        <v>-2683</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>DE334043640</t>
+          <t>DE293561563</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2411,23 +2411,23 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t xml:space="preserve">               395</t>
+          <t xml:space="preserve">               197</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>United Engineering Solutions GmbH</t>
+          <t>DS Crewing Sevices GmbH</t>
         </is>
       </c>
       <c r="C72" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="D72" t="n">
-        <v>0</v>
+        <v>-30</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>DE319531170</t>
+          <t>DE318346366</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2439,23 +2439,23 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t xml:space="preserve">               867</t>
+          <t xml:space="preserve">              1553</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>United Heavy Lift GmbH &amp; Co. KG</t>
+          <t>Davit-Company GmbH &amp; W. Harms</t>
         </is>
       </c>
       <c r="C73" t="n">
-        <v>-473</v>
+        <v>-96.31999999999999</v>
       </c>
       <c r="D73" t="n">
-        <v>-473</v>
+        <v>-96</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>DE350330845</t>
+          <t>DE291870147</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2467,23 +2467,23 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t xml:space="preserve">               637</t>
+          <t xml:space="preserve">              1169</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>over-C Crewing GmbH &amp; Co. KG</t>
+          <t>EMS Crewing GmbH</t>
         </is>
       </c>
       <c r="C74" t="n">
-        <v>-14</v>
+        <v>-146</v>
       </c>
       <c r="D74" t="n">
-        <v>-14</v>
+        <v>-146</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>DE321517652</t>
+          <t>DE262060886</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -2495,1398 +2495,2658 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3108</t>
+          <t xml:space="preserve">              2452</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Arion Greece S.A.</t>
+          <t>F.Laeisz GmbH Hamburg</t>
         </is>
       </c>
       <c r="C75" t="n">
-        <v>0</v>
+        <v>-53.6</v>
       </c>
       <c r="D75" t="n">
-        <v>0</v>
+        <v>-54</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>EL803103395</t>
+          <t>DE170925486</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t xml:space="preserve">               155</t>
+          <t xml:space="preserve">               231</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BLUE PLANET SHIPPING LTD</t>
+          <t>GP Care Solutions GmbH</t>
         </is>
       </c>
       <c r="C76" t="n">
-        <v>-15</v>
+        <v>-1540.93</v>
       </c>
       <c r="D76" t="n">
-        <v>-15</v>
+        <v>-1541</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>EL098093842</t>
+          <t>DE322179714</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t xml:space="preserve">               966</t>
+          <t xml:space="preserve">               601</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GIOVANTI TRAVEL S. A. MARKOU HOTEL AND TOURIST COM</t>
+          <t>GoodCrew GmbH</t>
         </is>
       </c>
       <c r="C77" t="n">
-        <v>-30</v>
+        <v>-2664.29</v>
       </c>
       <c r="D77" t="n">
-        <v>-30</v>
+        <v>-2664</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>EL095223487</t>
+          <t>DE326784905</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2315</t>
+          <t xml:space="preserve">              2284</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Marathon Airlines SA</t>
+          <t>Hansa Safety Services GmbH</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>-212.08</v>
+        <v>-1085.05</v>
       </c>
       <c r="D78" t="n">
-        <v>-212</v>
+        <v>-1085</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>EL800894668</t>
+          <t>DE284814823</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1058</t>
+          <t xml:space="preserve">              1146</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Power Sub Link SA</t>
+          <t>KG MS 2. CPO Livorno Offen Reederei GmbH &amp; Co. c/o</t>
         </is>
       </c>
       <c r="C79" t="n">
-        <v>-106</v>
+        <v>-25</v>
       </c>
       <c r="D79" t="n">
-        <v>-106</v>
+        <v>-25</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>EL800357365</t>
+          <t>DE322053391</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2103</t>
+          <t xml:space="preserve">              1145</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>ROKS MARITIME INC</t>
+          <t>KG MS CPO LA SPEZIA Offen Reederei UG (haftungsbes</t>
         </is>
       </c>
       <c r="C80" t="n">
-        <v>-42.4</v>
+        <v>-383</v>
       </c>
       <c r="D80" t="n">
-        <v>-42</v>
+        <v>-383</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>EL996795284</t>
+          <t>DE298771680</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t xml:space="preserve">               343</t>
+          <t xml:space="preserve">              2376</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Roxana Shipping S.A.</t>
+          <t>KG MS CPO VALENCIA Offen Reederei GmbH &amp; Co c/o CP</t>
         </is>
       </c>
       <c r="C81" t="n">
-        <v>228</v>
+        <v>-46</v>
       </c>
       <c r="D81" t="n">
-        <v>228</v>
+        <v>-46</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>EL098093983</t>
+          <t>DE257260686</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2295</t>
+          <t xml:space="preserve">              1144</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
+          <t>KG MS CPO VENEZIA Offen Reederei GmbH &amp; Co. c/o CP</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>-428.12</v>
+        <v>-186.61</v>
       </c>
       <c r="D82" t="n">
-        <v>-428</v>
+        <v>-187</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>EL801158466</t>
+          <t>DE256596537</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t xml:space="preserve">               896</t>
+          <t xml:space="preserve">              2015</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>SRS WHOLESALE (RE)INSURANCE BROKERS A.E.</t>
+          <t>KG MS Santa Viola Offen Reederei GmbH &amp; Co. c/o CP</t>
         </is>
       </c>
       <c r="C83" t="n">
-        <v>-1276.96</v>
+        <v>-25</v>
       </c>
       <c r="D83" t="n">
-        <v>-1277</v>
+        <v>-25</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>EL801153262</t>
+          <t>DE230140293</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2655</t>
+          <t xml:space="preserve">              1435</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>THALPIS CRS SA</t>
+          <t>M2L Pacific S.A.</t>
         </is>
       </c>
       <c r="C84" t="n">
-        <v>-175.72</v>
+        <v>-1596.11</v>
       </c>
       <c r="D84" t="n">
-        <v>-176</v>
+        <v>-1596</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>EL996435463</t>
+          <t>DE811585869</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2924</t>
+          <t xml:space="preserve">              1916</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>THENAMARIS CONBULK INC.</t>
+          <t>MS "Paganella 2" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C85" t="n">
-        <v>-21</v>
+        <v>-26.8</v>
       </c>
       <c r="D85" t="n">
-        <v>-21</v>
+        <v>-27</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>EL996795087</t>
+          <t>DE292632581</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2923</t>
+          <t xml:space="preserve">              1856</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Thenamaris LNG</t>
+          <t>MS "Pagna" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C86" t="n">
-        <v>-176.3</v>
+        <v>-75</v>
       </c>
       <c r="D86" t="n">
-        <v>-176</v>
+        <v>-75</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>EL997596883</t>
+          <t>DE261459100</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3021</t>
+          <t xml:space="preserve">              1548</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Velos Tankers Ltd.</t>
+          <t>MS "PolarPacific" GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C87" t="n">
-        <v>-9.99</v>
+        <v>-260.01</v>
       </c>
       <c r="D87" t="n">
-        <v>-10</v>
+        <v>-260</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>EL996864325</t>
+          <t>DE275633887</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Greece</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3111</t>
+          <t xml:space="preserve">              2859</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Arion Retail Group Hungary KFT</t>
+          <t>MS BSG Bimini GmbH &amp; Co.KG  c/o CPO Crewing GmbH &amp;</t>
         </is>
       </c>
       <c r="C88" t="n">
-        <v>-19.98</v>
+        <v>-25</v>
       </c>
       <c r="D88" t="n">
-        <v>-20</v>
+        <v>-25</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>HU32887413</t>
+          <t>DE346013071</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1952</t>
+          <t xml:space="preserve">              2684</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Fleet Air International Kft.</t>
+          <t>Martide Holding GmbH</t>
         </is>
       </c>
       <c r="C89" t="n">
-        <v>-390.83</v>
+        <v>16.52</v>
       </c>
       <c r="D89" t="n">
-        <v>-391</v>
+        <v>17</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>HU13819822</t>
+          <t>DE450210277</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Hungary</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2927</t>
+          <t xml:space="preserve">               309</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FLY4 Airlines Green Limited</t>
+          <t>NSB Crewing Solutions</t>
         </is>
       </c>
       <c r="C90" t="n">
-        <v>-3959.11</v>
+        <v>-4881.02</v>
       </c>
       <c r="D90" t="n">
-        <v>-3959</v>
+        <v>-4881</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>IE4197556QH</t>
+          <t>DE283269969</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t xml:space="preserve">               319</t>
+          <t xml:space="preserve">               310</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Pacific Blue Ltd</t>
+          <t>NSB Reederei GmbH &amp; Co. Kg</t>
         </is>
       </c>
       <c r="C91" t="n">
-        <v>-92.59999999999999</v>
+        <v>-843.41</v>
       </c>
       <c r="D91" t="n">
-        <v>-93</v>
+        <v>-843</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>IE6333494O</t>
+          <t>DE116474094</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Ireland</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2040</t>
+          <t xml:space="preserve">              2238</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
+          <t>Nordic Cruise Management GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C92" t="n">
-        <v>-253</v>
+        <v>-121.4</v>
       </c>
       <c r="D92" t="n">
-        <v>-253</v>
+        <v>-121</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>IT02122640994</t>
+          <t>DE362363142</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t xml:space="preserve">                85</t>
+          <t xml:space="preserve">               298</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Crewplanet SIA</t>
+          <t>Nordic Hamburg Crewing Services GmbH</t>
         </is>
       </c>
       <c r="C93" t="n">
-        <v>-24707.61</v>
+        <v>-31386</v>
       </c>
       <c r="D93" t="n">
-        <v>-24708</v>
+        <v>-31386</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>LV40003789592</t>
+          <t>DE309948810</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t xml:space="preserve">               340</t>
+          <t xml:space="preserve">              2678</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>RIX Shipmanagement LTD</t>
+          <t>Nordic Maritime Solutions GmbH &amp; CO. KG</t>
         </is>
       </c>
       <c r="C94" t="n">
-        <v>-5</v>
+        <v>-2397.4</v>
       </c>
       <c r="D94" t="n">
-        <v>-5</v>
+        <v>-2397</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>LV40103681236</t>
+          <t>DE285660591</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2420</t>
+          <t xml:space="preserve">              3088</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>SIA OJ Travel</t>
+          <t>Nordic Tokyo GmbH &amp; Co. KG c/o Nordic Cruise Manag</t>
         </is>
       </c>
       <c r="C95" t="n">
-        <v>-142.9</v>
+        <v>-182.4</v>
       </c>
       <c r="D95" t="n">
-        <v>-143</v>
+        <v>-182</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>LV40003286572</t>
+          <t>DE451301791</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1091</t>
+          <t xml:space="preserve">              3064</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>UNION AVIATION AS</t>
+          <t>OBC by Avico GmbH</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>-65.40000000000001</v>
+        <v>-573.39</v>
       </c>
       <c r="D96" t="n">
-        <v>-65</v>
+        <v>-573</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>LV40203294676</t>
+          <t>DE457137561</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Latvia</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2742</t>
+          <t xml:space="preserve">              3017</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>BALTNAUTIC SHIPPING LTD</t>
+          <t>SUNDAIR Gmbh</t>
         </is>
       </c>
       <c r="C97" t="n">
-        <v>-205.49</v>
+        <v>-192</v>
       </c>
       <c r="D97" t="n">
-        <v>-205</v>
+        <v>-192</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>LT417071917</t>
+          <t>DE305307186</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lithuania</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t xml:space="preserve">               569</t>
+          <t xml:space="preserve">               496</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>GEO@SEA Luxembourg S.A.</t>
+          <t>Scheibert &amp; Meissner Personalberatung GbR</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>-224.26</v>
+        <v>-75</v>
       </c>
       <c r="D98" t="n">
-        <v>-224</v>
+        <v>-75</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>LU32235384</t>
+          <t>DE240712065</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Luxembourg</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t xml:space="preserve">               862</t>
+          <t xml:space="preserve">              3026</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Atlantis Tankers Group (Malta) Ltd.</t>
+          <t>T &amp; T In Situ Machining GmbH</t>
         </is>
       </c>
       <c r="C99" t="n">
-        <v>-5</v>
+        <v>-543.9400000000001</v>
       </c>
       <c r="D99" t="n">
-        <v>-5</v>
+        <v>-544</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>MT21829715</t>
+          <t>DE327579122</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1465</t>
+          <t xml:space="preserve">               832</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>CldN Malta Ltd.</t>
+          <t>UHL Chartering GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C100" t="n">
-        <v>-668</v>
+        <v>-1446.3</v>
       </c>
       <c r="D100" t="n">
-        <v>-668</v>
+        <v>-1446</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>MT22140026</t>
+          <t>DE350330837</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2194</t>
+          <t xml:space="preserve">              1065</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Elit’Avia Malta Ltd</t>
+          <t>UHL Crewing GmbH</t>
         </is>
       </c>
       <c r="C101" t="n">
-        <v>-9.99</v>
+        <v>-5623.64</v>
       </c>
       <c r="D101" t="n">
-        <v>-10</v>
+        <v>-5624</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>MT19960414</t>
+          <t>DE330510394</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t xml:space="preserve">               218</t>
+          <t xml:space="preserve">               396</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>FT Portoria Tankers Ltd</t>
+          <t>USC Crew GmbH</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>-20</v>
+        <v>-10792.82</v>
       </c>
       <c r="D102" t="n">
-        <v>-20</v>
+        <v>-10793</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>MT22398518</t>
+          <t>DE274971782</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t xml:space="preserve">               718</t>
+          <t xml:space="preserve">              3065</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Furtrans Tanker Holdings Ltd</t>
+          <t>USC GmbH</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>-646.3499999999999</v>
+        <v>-2638.95</v>
       </c>
       <c r="D103" t="n">
-        <v>-646</v>
+        <v>-2639</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>MT26731101</t>
+          <t>DE334043640</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2408</t>
+          <t xml:space="preserve">               397</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Hans Travel Ltd</t>
+          <t>UVIS UG (haftungsbeschraenkt)</t>
         </is>
       </c>
       <c r="C104" t="n">
-        <v>250</v>
+        <v>-1187.48</v>
       </c>
       <c r="D104" t="n">
-        <v>250</v>
+        <v>-1187</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>MT28450014</t>
+          <t>DE319612386</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2939</t>
+          <t xml:space="preserve">               395</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Lighthouse Yachting Malta Limited</t>
+          <t>United Engineering Solutions GmbH</t>
         </is>
       </c>
       <c r="C105" t="n">
-        <v>-17.22</v>
+        <v>24</v>
       </c>
       <c r="D105" t="n">
-        <v>-17</v>
+        <v>24</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>MT29674336</t>
+          <t>DE319531170</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2037</t>
+          <t xml:space="preserve">               867</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
+          <t>United Heavy Lift GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>-313.99</v>
+        <v>-1667.09</v>
       </c>
       <c r="D106" t="n">
-        <v>-314</v>
+        <v>-1667</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>MT27270636</t>
+          <t>DE350330845</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2036</t>
+          <t xml:space="preserve">               637</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Quinto Tankers Ltd</t>
+          <t>over-C Crewing GmbH &amp; Co. KG</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>-36.28</v>
+        <v>-1203.67</v>
       </c>
       <c r="D107" t="n">
-        <v>-36</v>
+        <v>-1204</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>MT27591013</t>
+          <t>DE321517652</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Germany</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2105</t>
+          <t xml:space="preserve">              2295</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>ZuluWaves Limited</t>
+          <t>SPECIAL RISK SOLUTIONS (SRS) UNDERWRITING AGENCY M</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>-108.6</v>
+        <v>-281</v>
       </c>
       <c r="D108" t="n">
-        <v>-109</v>
+        <v>-281</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>MT30851503</t>
+          <t>EL801158466</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Malta</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t xml:space="preserve">               679</t>
+          <t xml:space="preserve">               896</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Afonso Ferreira Faria unipessoal LDa</t>
+          <t>SRS WHOLESALE (RE)INSURANCE BROKERS A.E.</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>-1874.48</v>
+        <v>-264</v>
       </c>
       <c r="D109" t="n">
-        <v>-1874</v>
+        <v>-264</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>PT513880151</t>
+          <t>EL801153262</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3008</t>
+          <t xml:space="preserve">              2655</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>JetUp, Lda.</t>
+          <t>THALPIS CRS SA</t>
         </is>
       </c>
       <c r="C110" t="n">
-        <v>-704</v>
+        <v>-117.69</v>
       </c>
       <c r="D110" t="n">
-        <v>-704</v>
+        <v>-118</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>PT518498298</t>
+          <t>EL996435463</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Greece</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1031</t>
+          <t xml:space="preserve">              3111</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
+          <t>Arion Retail Group Hungary KFT</t>
         </is>
       </c>
       <c r="C111" t="n">
-        <v>-862</v>
+        <v>-87.78</v>
       </c>
       <c r="D111" t="n">
-        <v>-862</v>
+        <v>-88</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>PT502635770</t>
+          <t>HU32887413</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2133</t>
+          <t xml:space="preserve">              1952</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Tulipa Mensageira LDA</t>
+          <t>Fleet Air International Kft.</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>0</v>
+        <v>-2080.78</v>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>-2081</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>PT517035863</t>
+          <t>HU13819822</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Portugal</t>
+          <t>Hungary</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t xml:space="preserve">              3109</t>
+          <t xml:space="preserve">              2486</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Arion Retail Group Romania S.R.L.</t>
+          <t>Alpha Marine</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>0</v>
+        <v>-325.4</v>
       </c>
       <c r="D113" t="n">
-        <v>0</v>
+        <v>-325</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>RO52745394</t>
+          <t>IE3417853KH</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1577</t>
+          <t xml:space="preserve">              2927</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>S.C. TOYO AVIATION S.R.L.</t>
+          <t>FLY4 Airlines Green Limited</t>
         </is>
       </c>
       <c r="C114" t="n">
-        <v>-51.2</v>
+        <v>-18409.84</v>
       </c>
       <c r="D114" t="n">
-        <v>-51</v>
+        <v>-18410</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>RO21977513</t>
+          <t>IE4197556QH</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Romania</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t xml:space="preserve">               420</t>
+          <t xml:space="preserve">               319</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Zumaia Offshore, S.L.</t>
+          <t>Pacific Blue Ltd</t>
         </is>
       </c>
       <c r="C115" t="n">
-        <v>-111.68</v>
+        <v>-5628.06</v>
       </c>
       <c r="D115" t="n">
-        <v>-112</v>
+        <v>-5628</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>ESB95442182</t>
+          <t>IE6333494O</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>SPAIN</t>
+          <t>Ireland</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t xml:space="preserve">               909</t>
+          <t xml:space="preserve">              2040</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ERZOFF-SHORE, S.L.</t>
+          <t>Furtrans Tanker &amp; Ship Management S.r.l</t>
         </is>
       </c>
       <c r="C116" t="n">
-        <v>-15.91</v>
+        <v>-581.6</v>
       </c>
       <c r="D116" t="n">
-        <v>-16</v>
+        <v>-582</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>ESB06919351</t>
+          <t>IT02122640994</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2471</t>
+          <t xml:space="preserve">              1529</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>C Survey</t>
+          <t>OMEGA S.R.L.</t>
         </is>
       </c>
       <c r="C117" t="n">
-        <v>-47.49</v>
+        <v>-47.75</v>
       </c>
       <c r="D117" t="n">
-        <v>-47</v>
+        <v>-48</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>SE556782721601</t>
+          <t>IT02343130270</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Italy</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t xml:space="preserve">               725</t>
+          <t xml:space="preserve">                34</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Linnea Shipping A/S</t>
+          <t>C Teleport AS</t>
         </is>
       </c>
       <c r="C118" t="n">
-        <v>-5</v>
+        <v>-228283.32</v>
       </c>
       <c r="D118" t="n">
-        <v>-5</v>
+        <v>-228283</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>SE556405820301</t>
+          <t>LV40203039827</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t xml:space="preserve">              2470</t>
+          <t xml:space="preserve">                85</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Manta Systems AB</t>
+          <t>Crewplanet SIA</t>
         </is>
       </c>
       <c r="C119" t="n">
-        <v>-95.84999999999999</v>
+        <v>-93718.46000000001</v>
       </c>
       <c r="D119" t="n">
-        <v>-96</v>
+        <v>-93718</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>SE559457660401</t>
+          <t>LV40003789592</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1437</t>
+          <t xml:space="preserve">               907</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Q Workforce</t>
+          <t>HANSAEL SIA</t>
         </is>
       </c>
       <c r="C120" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="D120" t="n">
-        <v>-5</v>
+        <v>-25</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>SE559200270201</t>
+          <t>LV40003660806</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1075</t>
+          <t xml:space="preserve">              2805</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rederi AB Donsötank - EUR</t>
+          <t>Martide Manning Latvia SIA</t>
         </is>
       </c>
       <c r="C121" t="n">
-        <v>-397</v>
+        <v>-198</v>
       </c>
       <c r="D121" t="n">
-        <v>-397</v>
+        <v>-198</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>SE556058292501</t>
+          <t>LV40203626599</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t xml:space="preserve">              1655</t>
+          <t xml:space="preserve">               340</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Sirius Shipping</t>
+          <t>RIX Shipmanagement LTD</t>
         </is>
       </c>
       <c r="C122" t="n">
-        <v>-448</v>
+        <v>-15969.25</v>
       </c>
       <c r="D122" t="n">
-        <v>-448</v>
+        <v>-15969</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>SE556772536001</t>
+          <t>LV40103681236</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t xml:space="preserve">               962</t>
+          <t xml:space="preserve">               751</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>VERITAS MANAGEMENT AB</t>
+          <t>SIA OJ CREW RIGA</t>
         </is>
       </c>
       <c r="C123" t="n">
-        <v>-67</v>
+        <v>25</v>
       </c>
       <c r="D123" t="n">
-        <v>-67</v>
+        <v>25</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>SE559003939101</t>
+          <t>LV50203144731</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Sweden</t>
+          <t>Latvia</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
+          <t xml:space="preserve">              2420</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>SIA OJ Travel</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>-15578.39</v>
+      </c>
+      <c r="D124" t="n">
+        <v>-15578</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>LV40003286572</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1091</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>UNION AVIATION AS</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>-8950.35</v>
+      </c>
+      <c r="D125" t="n">
+        <v>-8950</v>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>LV40203294676</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Latvia</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2742</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>BALTNAUTIC SHIPPING LTD</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>-1422.44</v>
+      </c>
+      <c r="D126" t="n">
+        <v>-1422</v>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>LT417071917</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Lithuania</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               569</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>GEO@SEA Luxembourg S.A.</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>-6290.82</v>
+      </c>
+      <c r="D127" t="n">
+        <v>-6291</v>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>LU32235384</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Luxembourg</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2964</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>MV KAREWOOD BRAVE — IMO 9281516</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>-60</v>
+      </c>
+      <c r="D128" t="n">
+        <v>-60</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>MT24502936</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>MALTA</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               862</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Atlantis Tankers Group (Malta) Ltd.</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>-344.24</v>
+      </c>
+      <c r="D129" t="n">
+        <v>-344</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>MT21829715</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1465</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>CldN Malta Ltd.</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>-28320.51</v>
+      </c>
+      <c r="D130" t="n">
+        <v>-28321</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>MT22140026</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1415</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>DC Aviation Ltd.</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>-1023.68</v>
+      </c>
+      <c r="D131" t="n">
+        <v>-1024</v>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>MT18886308</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2194</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Elit’Avia Malta Ltd</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>-5560.25</v>
+      </c>
+      <c r="D132" t="n">
+        <v>-5560</v>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>MT19960414</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               218</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>FT Portoria Tankers Ltd</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>-351.6</v>
+      </c>
+      <c r="D133" t="n">
+        <v>-352</v>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>MT22398518</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               718</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Furtrans Tanker Holdings Ltd</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>-2381.7</v>
+      </c>
+      <c r="D134" t="n">
+        <v>-2382</v>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>MT26731101</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2408</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Hans Travel Ltd</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>250</v>
+      </c>
+      <c r="D135" t="n">
+        <v>250</v>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>MT28450014</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2939</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Lighthouse Yachting Malta Limited</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>-246.52</v>
+      </c>
+      <c r="D136" t="n">
+        <v>-247</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>MT29674336</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2963</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>MV KAREWOOD GLORY — IMO 9281504</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>-177.78</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-178</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>MT24503928</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2995</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>MV KAREWOOD PRIDE — IMO 9281499</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>-90</v>
+      </c>
+      <c r="D138" t="n">
+        <v>-90</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>MT24503035</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2992</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>MV KAREWOOD STAR — IMO 9363986</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>-107.81</v>
+      </c>
+      <c r="D139" t="n">
+        <v>-108</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>MT24503217</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2037</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Quarto Tankers Ltd  - 25/16 Vincenti Buildings</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>-1030.85</v>
+      </c>
+      <c r="D140" t="n">
+        <v>-1031</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>MT27270636</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2036</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Quinto Tankers Ltd</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>-535.17</v>
+      </c>
+      <c r="D141" t="n">
+        <v>-535</v>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>MT27591013</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               826</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>SL Ship Management Ltd</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>-1589.04</v>
+      </c>
+      <c r="D142" t="n">
+        <v>-1589</v>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>MT18726720</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2105</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>ZuluWaves Limited</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>-2410.24</v>
+      </c>
+      <c r="D143" t="n">
+        <v>-2410</v>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>MT30851503</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Malta</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              3110</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Arion Retail Group Poland Sp. z o.o.</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>-18</v>
+      </c>
+      <c r="D144" t="n">
+        <v>-18</v>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>PL5253064487</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Poland</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               679</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>Afonso Ferreira Faria unipessoal LDa</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>-4531.1</v>
+      </c>
+      <c r="D145" t="n">
+        <v>-4531</v>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>PT513880151</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              3008</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>JetUp, Lda.</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>-1383</v>
+      </c>
+      <c r="D146" t="n">
+        <v>-1383</v>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>PT518498298</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1031</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>S&amp;C - Gestão de Navios e Tripulações, Lda.</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>-1302.34</v>
+      </c>
+      <c r="D147" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>PT502635770</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2133</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>Tulipa Mensageira LDA</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>-3732.06</v>
+      </c>
+      <c r="D148" t="n">
+        <v>-3732</v>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>PT517035863</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>Portugal</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              3109</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>Arion Retail Group Romania S.R.L.</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>2.664535259100376e-15</v>
+      </c>
+      <c r="D149" t="n">
+        <v>0</v>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>RO52745394</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2097</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>JET ADVISOR</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>-268.3</v>
+      </c>
+      <c r="D150" t="n">
+        <v>-268</v>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>RO28308419</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1577</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>S.C. TOYO AVIATION S.R.L.</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>-2950.35</v>
+      </c>
+      <c r="D151" t="n">
+        <v>-2950</v>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>RO21977513</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>Romania</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               420</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Zumaia Offshore, S.L.</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>-1529.27</v>
+      </c>
+      <c r="D152" t="n">
+        <v>-1529</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>ESB95442182</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>SPAIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               909</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>ERZOFF-SHORE, S.L.</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>-83.71000000000001</v>
+      </c>
+      <c r="D153" t="n">
+        <v>-84</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>ESB06919351</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2236</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Espana Rope Access Solutions SL</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>-2593.03</v>
+      </c>
+      <c r="D154" t="n">
+        <v>-2593</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>ESB09880675</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2389</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Geoxyz Spain SL</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>-218.34</v>
+      </c>
+      <c r="D155" t="n">
+        <v>-218</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>ESB13905591</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2471</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>C Survey</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>-529.09</v>
+      </c>
+      <c r="D156" t="n">
+        <v>-529</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>SE556782721601</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2670</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Fjordtank Rederi AB</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>-551.21</v>
+      </c>
+      <c r="D157" t="n">
+        <v>-551</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>SE556633100401</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              3135</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>FureBear AB</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>-30</v>
+      </c>
+      <c r="D158" t="n">
+        <v>-30</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>SE559389323201</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              3133</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Furetank Rederi AB</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>-316.69</v>
+      </c>
+      <c r="D159" t="n">
+        <v>-317</v>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>SE556371751001</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2692</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>HF Interior AB</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>-559.29</v>
+      </c>
+      <c r="D160" t="n">
+        <v>-559</v>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>SE556844774101</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               725</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>Linnea Shipping A/S</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>-2777.19</v>
+      </c>
+      <c r="D161" t="n">
+        <v>-2777</v>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>SE556405820301</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2470</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>Manta Systems AB</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>-348.08</v>
+      </c>
+      <c r="D162" t="n">
+        <v>-348</v>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>SE559457660401</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               616</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>OljOla Shipping AB</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>-339.67</v>
+      </c>
+      <c r="D163" t="n">
+        <v>-340</v>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>SE559151957301</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1437</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Q Workforce</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>-921.9</v>
+      </c>
+      <c r="D164" t="n">
+        <v>-922</v>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>SE559200270201</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1075</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>Rederi AB Donsötank - EUR</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>-4743.49</v>
+      </c>
+      <c r="D165" t="n">
+        <v>-4743</v>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>SE556058292501</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              2735</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>Sirius Agency</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>50</v>
+      </c>
+      <c r="D166" t="n">
+        <v>50</v>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>SE556043575101</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t xml:space="preserve">              1655</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Sirius Shipping</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>-7556.64</v>
+      </c>
+      <c r="D167" t="n">
+        <v>-7557</v>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>SE556772536001</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t xml:space="preserve">               962</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>VERITAS MANAGEMENT AB</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>-2697.02</v>
+      </c>
+      <c r="D168" t="n">
+        <v>-2697</v>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>SE559003939101</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Sweden</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
           <t xml:space="preserve">              2580</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
+      <c r="B169" t="inlineStr">
         <is>
           <t>West Atlantic Sweden AB</t>
         </is>
       </c>
-      <c r="C124" t="n">
-        <v>-104</v>
-      </c>
-      <c r="D124" t="n">
-        <v>-104</v>
-      </c>
-      <c r="E124" t="inlineStr">
+      <c r="C169" t="n">
+        <v>-2523.14</v>
+      </c>
+      <c r="D169" t="n">
+        <v>-2523</v>
+      </c>
+      <c r="E169" t="inlineStr">
         <is>
           <t>SE556062442001</t>
         </is>
       </c>
-      <c r="F124" t="inlineStr">
+      <c r="F169" t="inlineStr">
         <is>
           <t>Sweden</t>
         </is>
